--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Mode-emploi" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="306">
   <si>
     <t>id</t>
   </si>
@@ -925,6 +925,24 @@
   </si>
   <si>
     <t>Arbre_93_2025-10-10.jpg</t>
+  </si>
+  <si>
+    <t>Pas repris suite manque d'arrosage pendant été 2025</t>
+  </si>
+  <si>
+    <t>Paris Bonsai Expo 2025</t>
+  </si>
+  <si>
+    <t>Arbre_94_2025-11-07.jpg</t>
+  </si>
+  <si>
+    <t>Serissa Japonica</t>
+  </si>
+  <si>
+    <t>Rubiacées</t>
+  </si>
+  <si>
+    <t>Arbre_47_2025-11-07-deligature.jpg</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1198,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -3967,6 +3985,35 @@
       </c>
       <c r="T94" t="s">
         <v>299</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="C95" t="s">
+        <v>303</v>
+      </c>
+      <c r="D95" t="s">
+        <v>304</v>
+      </c>
+      <c r="F95" t="s">
+        <v>112</v>
+      </c>
+      <c r="G95" t="s">
+        <v>164</v>
+      </c>
+      <c r="H95" s="2">
+        <v>45962</v>
+      </c>
+      <c r="J95" s="9">
+        <v>25</v>
+      </c>
+      <c r="R95" t="s">
+        <v>301</v>
+      </c>
+      <c r="T95" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +4037,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -5636,6 +5683,37 @@
         <v>294</v>
       </c>
     </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>76</v>
+      </c>
+      <c r="B117" s="2">
+        <v>45886</v>
+      </c>
+      <c r="C117" t="s">
+        <v>259</v>
+      </c>
+      <c r="D117" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>47</v>
+      </c>
+      <c r="B118" s="2">
+        <v>45966</v>
+      </c>
+      <c r="C118" t="s">
+        <v>134</v>
+      </c>
+      <c r="D118" t="s">
+        <v>293</v>
+      </c>
+      <c r="E118" t="s">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mode-emploi" sheetId="3" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="actions" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">actions!$A$1:$E$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">bonsais!$A$1:$U$92</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="310">
   <si>
     <t>id</t>
   </si>
@@ -270,9 +271,6 @@
   </si>
   <si>
     <t>Arbre_70_2024-11-25.jpeg</t>
-  </si>
-  <si>
-    <t>Arbre_71_2024-11-25.jpeg</t>
   </si>
   <si>
     <t>Arbre_8_2024-11-17.jpeg</t>
@@ -943,6 +941,21 @@
   </si>
   <si>
     <t>Arbre_47_2025-11-07-deligature.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_47_2025-11-07-pot.jpg</t>
+  </si>
+  <si>
+    <t>Callicarpa</t>
+  </si>
+  <si>
+    <t>Hyper U</t>
+  </si>
+  <si>
+    <t>Arbre_95_2025-11-15.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_66_2025-11-15_rempotage.jpg</t>
   </si>
 </sst>
 </file>
@@ -1180,12 +1193,12 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1198,7 +1211,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:T96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -1235,25 +1248,25 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K1" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="L1" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="L1" s="15" t="s">
-        <v>265</v>
-      </c>
       <c r="M1" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N1" s="16" t="s">
         <v>3</v>
@@ -1265,7 +1278,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>4</v>
@@ -1282,13 +1295,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H2" s="17">
         <v>44982</v>
@@ -1311,16 +1324,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H3" s="17">
         <v>45591</v>
@@ -1343,13 +1356,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H4" s="17">
         <v>45041</v>
@@ -1372,16 +1385,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H5" s="17">
         <v>45339</v>
@@ -1395,7 +1408,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="S5" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>48</v>
@@ -1406,13 +1419,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H6" s="17"/>
       <c r="J6" s="12"/>
@@ -1432,16 +1445,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="H7" s="17">
         <v>45200</v>
@@ -1465,16 +1478,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="H8" s="17">
         <v>44835</v>
@@ -1496,16 +1509,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H9" s="17">
         <v>45041</v>
@@ -1519,7 +1532,7 @@
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
       <c r="T9" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1527,16 +1540,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="H10" s="2">
         <v>44842</v>
@@ -1547,7 +1560,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="T10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1555,19 +1568,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
@@ -1586,16 +1599,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
@@ -1606,7 +1619,7 @@
         <v>2024</v>
       </c>
       <c r="S12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T12" t="s">
         <v>17</v>
@@ -1617,13 +1630,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
@@ -1642,19 +1655,19 @@
         <v>13</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
@@ -1673,19 +1686,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="H15" s="2">
         <v>45535</v>
@@ -1704,19 +1717,19 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" t="s">
         <v>161</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>162</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" t="s">
         <v>163</v>
-      </c>
-      <c r="F16" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" t="s">
-        <v>164</v>
       </c>
       <c r="H16" s="2">
         <v>45591</v>
@@ -1730,7 +1743,7 @@
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T16" t="s">
         <v>21</v>
@@ -1741,16 +1754,16 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
+        <v>184</v>
+      </c>
+      <c r="F17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" t="s">
         <v>189</v>
-      </c>
-      <c r="E17" t="s">
-        <v>185</v>
-      </c>
-      <c r="F17" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" t="s">
-        <v>190</v>
       </c>
       <c r="J17" s="9">
         <v>10</v>
@@ -1772,13 +1785,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" t="s">
         <v>191</v>
-      </c>
-      <c r="F18" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" t="s">
-        <v>192</v>
       </c>
       <c r="H18" s="2">
         <v>45261</v>
@@ -1803,10 +1816,10 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
@@ -1822,13 +1835,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2">
         <v>44982</v>
@@ -1847,13 +1860,13 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" t="s">
         <v>194</v>
-      </c>
-      <c r="F21" t="s">
-        <v>112</v>
-      </c>
-      <c r="G21" t="s">
-        <v>195</v>
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
@@ -1869,13 +1882,13 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
@@ -1891,13 +1904,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J23" s="9">
         <v>50</v>
@@ -1911,7 +1924,7 @@
         <v>-0.5</v>
       </c>
       <c r="S23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="T23" t="s">
         <v>29</v>
@@ -1922,16 +1935,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" t="s">
         <v>142</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="F24" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" t="s">
-        <v>143</v>
       </c>
       <c r="H24" s="2">
         <v>45339</v>
@@ -1953,13 +1966,13 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
+        <v>197</v>
+      </c>
+      <c r="F25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" t="s">
         <v>198</v>
-      </c>
-      <c r="F25" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" t="s">
-        <v>199</v>
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
@@ -1978,16 +1991,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H26" s="2">
         <v>45584</v>
@@ -2001,7 +2014,7 @@
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
       <c r="R26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T26" t="s">
         <v>32</v>
@@ -2012,16 +2025,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H27" s="2">
         <v>45584</v>
@@ -2035,7 +2048,7 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
       <c r="R27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T27" t="s">
         <v>33</v>
@@ -2046,13 +2059,13 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2">
         <v>45413</v>
@@ -2066,7 +2079,7 @@
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
       <c r="R28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T28" t="s">
         <v>34</v>
@@ -2077,22 +2090,22 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H29" s="2">
         <v>45420</v>
       </c>
       <c r="I29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J29" s="9">
         <v>100</v>
@@ -2111,16 +2124,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D30" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" t="s">
         <v>205</v>
-      </c>
-      <c r="F30" t="s">
-        <v>112</v>
-      </c>
-      <c r="G30" t="s">
-        <v>206</v>
       </c>
       <c r="H30" s="2">
         <v>44982</v>
@@ -2134,7 +2147,7 @@
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
       <c r="S30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T30" t="s">
         <v>36</v>
@@ -2145,16 +2158,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" t="s">
         <v>207</v>
-      </c>
-      <c r="D31" t="s">
-        <v>205</v>
-      </c>
-      <c r="F31" t="s">
-        <v>115</v>
-      </c>
-      <c r="G31" t="s">
-        <v>208</v>
       </c>
       <c r="J31" s="9">
         <v>30</v>
@@ -2176,19 +2189,19 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D32" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" t="s">
         <v>205</v>
-      </c>
-      <c r="E32" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32" t="s">
-        <v>206</v>
       </c>
       <c r="H32" s="2">
         <v>45339</v>
@@ -2202,10 +2215,10 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
       <c r="R32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T32" t="s">
         <v>39</v>
@@ -2216,19 +2229,19 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" t="s">
         <v>205</v>
-      </c>
-      <c r="E33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" t="s">
-        <v>206</v>
       </c>
       <c r="H33" s="2">
         <v>45339</v>
@@ -2242,10 +2255,10 @@
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
       <c r="R33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T33" t="s">
         <v>40</v>
@@ -2256,13 +2269,13 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" t="s">
+        <v>132</v>
+      </c>
+      <c r="G34" t="s">
         <v>210</v>
-      </c>
-      <c r="F34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G34" t="s">
-        <v>211</v>
       </c>
       <c r="H34" s="2">
         <v>44896</v>
@@ -2281,13 +2294,13 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H35" s="2">
         <v>45339</v>
@@ -2309,13 +2322,13 @@
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H36" s="2">
         <v>44982</v>
@@ -2326,7 +2339,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
       <c r="S36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="T36" t="s">
         <v>43</v>
@@ -2337,13 +2350,13 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" t="s">
         <v>215</v>
-      </c>
-      <c r="F37" t="s">
-        <v>115</v>
-      </c>
-      <c r="G37" t="s">
-        <v>216</v>
       </c>
       <c r="H37" s="2">
         <v>45200</v>
@@ -2365,13 +2378,13 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" t="s">
         <v>217</v>
-      </c>
-      <c r="F38" t="s">
-        <v>112</v>
-      </c>
-      <c r="G38" t="s">
-        <v>218</v>
       </c>
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
@@ -2390,13 +2403,13 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H39" s="2">
         <v>44982</v>
@@ -2418,10 +2431,10 @@
         <v>39</v>
       </c>
       <c r="F40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
@@ -2429,10 +2442,10 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
       <c r="R40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="T40" t="s">
         <v>47</v>
@@ -2443,16 +2456,16 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H41" s="2">
         <v>45041</v>
@@ -2474,13 +2487,13 @@
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H42" s="2">
         <v>45041</v>
@@ -2502,13 +2515,13 @@
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G43" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H43" s="2">
         <v>45200</v>
@@ -2530,16 +2543,16 @@
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E44" t="s">
+        <v>219</v>
+      </c>
+      <c r="F44" t="s">
+        <v>114</v>
+      </c>
+      <c r="G44" t="s">
         <v>220</v>
-      </c>
-      <c r="F44" t="s">
-        <v>115</v>
-      </c>
-      <c r="G44" t="s">
-        <v>221</v>
       </c>
       <c r="H44" s="2">
         <v>45200</v>
@@ -2561,16 +2574,16 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H45" s="2">
         <v>44896</v>
@@ -2589,13 +2602,13 @@
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H46" s="2">
         <v>44989</v>
@@ -2617,13 +2630,13 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J47" s="9">
         <v>0</v>
@@ -2645,13 +2658,13 @@
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H48" s="2">
         <v>45206</v>
@@ -2673,10 +2686,10 @@
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J49" s="9">
         <v>0</v>
@@ -2690,7 +2703,7 @@
         <v>2023</v>
       </c>
       <c r="S49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T49" t="s">
         <v>57</v>
@@ -2701,13 +2714,13 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H50" s="2">
         <v>45206</v>
@@ -2729,13 +2742,13 @@
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H51" s="2">
         <v>45206</v>
@@ -2757,13 +2770,13 @@
         <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J52" s="9">
         <v>0</v>
@@ -2785,16 +2798,16 @@
         <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H53" s="2">
         <v>45206</v>
@@ -2816,13 +2829,13 @@
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H54" s="2">
         <v>45971</v>
@@ -2836,7 +2849,7 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="11"/>
       <c r="R54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T54" t="s">
         <v>63</v>
@@ -2847,13 +2860,13 @@
         <v>54</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H55" s="21">
         <v>45207</v>
@@ -2880,13 +2893,13 @@
         <v>55</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H56" s="2">
         <v>45206</v>
@@ -2908,19 +2921,19 @@
         <v>57</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H57" s="2">
         <v>45971</v>
@@ -2942,16 +2955,16 @@
         <v>58</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H58" s="2">
         <v>45971</v>
@@ -2973,16 +2986,16 @@
         <v>59</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H59" s="2">
         <v>45971</v>
@@ -3004,13 +3017,13 @@
         <v>60</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H60" s="2">
         <v>45206</v>
@@ -3032,13 +3045,13 @@
         <v>61</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H61" s="2">
         <v>45206</v>
@@ -3060,13 +3073,13 @@
         <v>62</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H62" s="2">
         <v>45206</v>
@@ -3088,13 +3101,13 @@
         <v>63</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J63" s="9">
         <v>0</v>
@@ -3105,7 +3118,7 @@
       <c r="P63" s="11"/>
       <c r="Q63" s="11"/>
       <c r="R63" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T63" t="s">
         <v>73</v>
@@ -3116,13 +3129,13 @@
         <v>64</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J64" s="9">
         <v>0</v>
@@ -3133,10 +3146,10 @@
       <c r="P64" s="11"/>
       <c r="Q64" s="11"/>
       <c r="R64" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T64" t="s">
         <v>74</v>
@@ -3147,16 +3160,16 @@
         <v>65</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H65" s="2">
         <v>44989</v>
@@ -3178,13 +3191,13 @@
         <v>66</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H66" s="2">
         <v>44989</v>
@@ -3206,13 +3219,13 @@
         <v>67</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H67" s="2">
         <v>44989</v>
@@ -3234,13 +3247,13 @@
         <v>68</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H68" s="2">
         <v>44989</v>
@@ -3262,13 +3275,13 @@
         <v>69</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H69" s="2">
         <v>44989</v>
@@ -3290,16 +3303,16 @@
         <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H70" s="2">
         <v>45626</v>
@@ -3322,16 +3335,16 @@
         <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H71" s="2">
         <v>45626</v>
@@ -3346,7 +3359,7 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="11"/>
       <c r="T71" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -3354,13 +3367,13 @@
         <v>72</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
       </c>
       <c r="G72" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H72" s="2">
         <v>45662</v>
@@ -3375,7 +3388,7 @@
       <c r="P72" s="11"/>
       <c r="Q72" s="11"/>
       <c r="T72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -3383,13 +3396,13 @@
         <v>73</v>
       </c>
       <c r="D73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H73" s="2">
         <v>45675</v>
@@ -3404,7 +3417,7 @@
       <c r="P73" s="11"/>
       <c r="Q73" s="11"/>
       <c r="T73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -3412,10 +3425,10 @@
         <v>74</v>
       </c>
       <c r="D74" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H74" s="2">
         <v>45675</v>
@@ -3430,7 +3443,7 @@
       <c r="P74" s="11"/>
       <c r="Q74" s="11"/>
       <c r="T74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -3438,13 +3451,13 @@
         <v>75</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H75" s="2">
         <v>45675</v>
@@ -3456,7 +3469,7 @@
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="T75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -3464,16 +3477,16 @@
         <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H76" s="2">
         <v>45710</v>
@@ -3483,7 +3496,7 @@
         <v>185</v>
       </c>
       <c r="T76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -3491,28 +3504,28 @@
         <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H77" s="2">
         <v>45710</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J77" s="9">
         <v>70</v>
       </c>
       <c r="T77" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -3520,34 +3533,34 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H78" s="2">
         <v>45710</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J78" s="9">
         <v>140</v>
       </c>
       <c r="R78" t="s">
+        <v>129</v>
+      </c>
+      <c r="S78" t="s">
         <v>130</v>
       </c>
-      <c r="S78" t="s">
-        <v>131</v>
-      </c>
       <c r="T78" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -3555,28 +3568,28 @@
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G79" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H79" s="2">
         <v>45710</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J79" s="9">
         <v>35</v>
       </c>
       <c r="T79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -3584,13 +3597,13 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
+        <v>131</v>
+      </c>
+      <c r="F80" t="s">
         <v>132</v>
       </c>
-      <c r="F80" t="s">
-        <v>133</v>
-      </c>
       <c r="G80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H80" s="2">
         <v>45710</v>
@@ -3599,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="R80" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T80" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -3610,16 +3623,16 @@
         <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D81" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H81" s="2">
         <v>45774</v>
@@ -3628,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="T81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -3636,16 +3649,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" t="s">
+        <v>248</v>
+      </c>
+      <c r="F82" t="s">
+        <v>132</v>
+      </c>
+      <c r="G82" t="s">
         <v>249</v>
-      </c>
-      <c r="D82" t="s">
-        <v>249</v>
-      </c>
-      <c r="F82" t="s">
-        <v>133</v>
-      </c>
-      <c r="G82" t="s">
-        <v>250</v>
       </c>
       <c r="H82" s="2">
         <v>45774</v>
@@ -3654,10 +3667,10 @@
         <v>0</v>
       </c>
       <c r="R82" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T82" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -3665,16 +3678,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H83" s="2">
         <v>45774</v>
@@ -3683,10 +3696,10 @@
         <v>5</v>
       </c>
       <c r="R83" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T83" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -3694,19 +3707,19 @@
         <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F84" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G84" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H84" s="2">
         <v>45774</v>
@@ -3715,10 +3728,10 @@
         <v>2</v>
       </c>
       <c r="R84" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T84" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -3726,13 +3739,13 @@
         <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F85" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H85" s="2">
         <v>45794</v>
@@ -3741,10 +3754,10 @@
         <v>45</v>
       </c>
       <c r="R85" t="s">
+        <v>268</v>
+      </c>
+      <c r="T85" t="s">
         <v>269</v>
-      </c>
-      <c r="T85" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -3752,16 +3765,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D86" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F86" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G86" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H86" s="2">
         <v>45794</v>
@@ -3770,10 +3783,10 @@
         <v>50</v>
       </c>
       <c r="R86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T86" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -3781,16 +3794,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
+        <v>271</v>
+      </c>
+      <c r="D87" t="s">
+        <v>116</v>
+      </c>
+      <c r="F87" t="s">
+        <v>111</v>
+      </c>
+      <c r="G87" t="s">
         <v>272</v>
-      </c>
-      <c r="D87" t="s">
-        <v>117</v>
-      </c>
-      <c r="F87" t="s">
-        <v>112</v>
-      </c>
-      <c r="G87" t="s">
-        <v>273</v>
       </c>
       <c r="H87" s="2">
         <v>45794</v>
@@ -3799,10 +3812,10 @@
         <v>70</v>
       </c>
       <c r="R87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -3810,16 +3823,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D88" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F88" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H88" s="2">
         <v>45809</v>
@@ -3828,10 +3841,10 @@
         <v>10</v>
       </c>
       <c r="R88" t="s">
+        <v>275</v>
+      </c>
+      <c r="T88" t="s">
         <v>276</v>
-      </c>
-      <c r="T88" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -3839,16 +3852,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F89" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H89" s="2">
         <v>45808</v>
@@ -3857,10 +3870,10 @@
         <v>40</v>
       </c>
       <c r="R89" t="s">
+        <v>277</v>
+      </c>
+      <c r="T89" t="s">
         <v>278</v>
-      </c>
-      <c r="T89" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -3868,13 +3881,13 @@
         <v>89</v>
       </c>
       <c r="D90" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H90" s="2">
         <v>45808</v>
@@ -3883,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="R90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T90" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -3894,13 +3907,13 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G91" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H91" s="2">
         <v>45824</v>
@@ -3909,7 +3922,7 @@
         <v>3.99</v>
       </c>
       <c r="T91" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -3917,16 +3930,16 @@
         <v>91</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F92" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G92" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H92" s="2">
         <v>45830</v>
@@ -3935,7 +3948,7 @@
         <v>100</v>
       </c>
       <c r="T92" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -3943,16 +3956,16 @@
         <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D93" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G93" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H93" s="2">
         <v>45927</v>
@@ -3961,7 +3974,7 @@
         <v>5</v>
       </c>
       <c r="T93" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -3969,13 +3982,13 @@
         <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H94" s="2">
         <v>45927</v>
@@ -3984,7 +3997,7 @@
         <v>10</v>
       </c>
       <c r="T94" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -3992,16 +4005,16 @@
         <v>94</v>
       </c>
       <c r="C95" t="s">
+        <v>302</v>
+      </c>
+      <c r="D95" t="s">
         <v>303</v>
       </c>
-      <c r="D95" t="s">
-        <v>304</v>
-      </c>
       <c r="F95" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G95" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H95" s="2">
         <v>45962</v>
@@ -4010,10 +4023,33 @@
         <v>25</v>
       </c>
       <c r="R95" t="s">
+        <v>300</v>
+      </c>
+      <c r="T95" t="s">
         <v>301</v>
       </c>
-      <c r="T95" t="s">
-        <v>302</v>
+    </row>
+    <row r="96" spans="1:20">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="C96" t="s">
+        <v>306</v>
+      </c>
+      <c r="F96" t="s">
+        <v>111</v>
+      </c>
+      <c r="G96" t="s">
+        <v>307</v>
+      </c>
+      <c r="H96" s="2">
+        <v>45976</v>
+      </c>
+      <c r="J96" s="9">
+        <v>9.99</v>
+      </c>
+      <c r="T96" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -4034,10 +4070,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -4049,22 +4085,22 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="5" customFormat="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -4072,16 +4108,16 @@
         <v>45364</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -4089,16 +4125,16 @@
         <v>45458</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="5" customFormat="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -4106,16 +4142,16 @@
         <v>45189</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="5" customFormat="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -4123,16 +4159,16 @@
         <v>45620</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="5" customFormat="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -4143,13 +4179,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="5" customFormat="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -4160,21 +4196,21 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="5" customFormat="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="5" customFormat="1" hidden="1">
       <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:5" hidden="1">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4182,13 +4218,13 @@
         <v>45613</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4196,13 +4232,13 @@
         <v>45613</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1">
       <c r="A11">
         <v>3</v>
       </c>
@@ -4210,13 +4246,13 @@
         <v>45613</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1">
       <c r="A12">
         <v>4</v>
       </c>
@@ -4224,13 +4260,13 @@
         <v>45613</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1">
       <c r="A13">
         <v>5</v>
       </c>
@@ -4238,13 +4274,13 @@
         <v>45613</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1">
       <c r="A14">
         <v>6</v>
       </c>
@@ -4252,13 +4288,13 @@
         <v>45613</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1">
       <c r="A15">
         <v>7</v>
       </c>
@@ -4266,13 +4302,13 @@
         <v>45613</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1">
       <c r="A16">
         <v>8</v>
       </c>
@@ -4280,13 +4316,13 @@
         <v>45613</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1">
       <c r="A17">
         <v>9</v>
       </c>
@@ -4294,13 +4330,13 @@
         <v>45613</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1">
       <c r="A18">
         <v>10</v>
       </c>
@@ -4308,13 +4344,13 @@
         <v>45613</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1">
       <c r="A19">
         <v>11</v>
       </c>
@@ -4322,13 +4358,13 @@
         <v>45613</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1">
       <c r="A20">
         <v>12</v>
       </c>
@@ -4336,13 +4372,13 @@
         <v>45613</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1">
       <c r="A21">
         <v>13</v>
       </c>
@@ -4350,13 +4386,13 @@
         <v>45613</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1">
       <c r="A22">
         <v>14</v>
       </c>
@@ -4364,13 +4400,13 @@
         <v>45613</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1">
       <c r="A23">
         <v>15</v>
       </c>
@@ -4378,13 +4414,13 @@
         <v>45613</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1">
       <c r="A24">
         <v>16</v>
       </c>
@@ -4392,13 +4428,13 @@
         <v>45613</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1">
       <c r="A25">
         <v>17</v>
       </c>
@@ -4406,13 +4442,13 @@
         <v>45613</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1">
       <c r="A26">
         <v>18</v>
       </c>
@@ -4420,13 +4456,13 @@
         <v>45613</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1">
       <c r="A27">
         <v>19</v>
       </c>
@@ -4434,13 +4470,13 @@
         <v>45613</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" hidden="1">
       <c r="A28">
         <v>20</v>
       </c>
@@ -4448,13 +4484,13 @@
         <v>45613</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1">
       <c r="A29">
         <v>21</v>
       </c>
@@ -4462,13 +4498,13 @@
         <v>45613</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1">
       <c r="A30">
         <v>22</v>
       </c>
@@ -4476,13 +4512,13 @@
         <v>45613</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" hidden="1">
       <c r="A31">
         <v>23</v>
       </c>
@@ -4490,13 +4526,13 @@
         <v>45613</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1">
       <c r="A32">
         <v>24</v>
       </c>
@@ -4504,13 +4540,13 @@
         <v>45613</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" hidden="1">
       <c r="A33">
         <v>25</v>
       </c>
@@ -4518,13 +4554,13 @@
         <v>45613</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1">
       <c r="A34">
         <v>26</v>
       </c>
@@ -4532,13 +4568,13 @@
         <v>45613</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1">
       <c r="A35">
         <v>27</v>
       </c>
@@ -4546,13 +4582,13 @@
         <v>45613</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1">
       <c r="A36">
         <v>28</v>
       </c>
@@ -4560,13 +4596,13 @@
         <v>45613</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1">
       <c r="A37">
         <v>29</v>
       </c>
@@ -4574,13 +4610,13 @@
         <v>45613</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1">
       <c r="A38">
         <v>30</v>
       </c>
@@ -4588,13 +4624,13 @@
         <v>45613</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1">
       <c r="A39">
         <v>31</v>
       </c>
@@ -4602,13 +4638,13 @@
         <v>45613</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1">
       <c r="A40">
         <v>32</v>
       </c>
@@ -4616,13 +4652,13 @@
         <v>45613</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1">
       <c r="A41">
         <v>33</v>
       </c>
@@ -4630,13 +4666,13 @@
         <v>45613</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1">
       <c r="A42">
         <v>34</v>
       </c>
@@ -4644,13 +4680,13 @@
         <v>45613</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" hidden="1">
       <c r="A43">
         <v>35</v>
       </c>
@@ -4658,13 +4694,13 @@
         <v>45613</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1">
       <c r="A44">
         <v>36</v>
       </c>
@@ -4672,13 +4708,13 @@
         <v>45613</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1">
       <c r="A45">
         <v>37</v>
       </c>
@@ -4686,13 +4722,13 @@
         <v>45613</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" hidden="1">
       <c r="A46">
         <v>38</v>
       </c>
@@ -4700,13 +4736,13 @@
         <v>45613</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1">
       <c r="A47">
         <v>39</v>
       </c>
@@ -4714,13 +4750,13 @@
         <v>45613</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" hidden="1">
       <c r="A48">
         <v>40</v>
       </c>
@@ -4728,13 +4764,13 @@
         <v>45613</v>
       </c>
       <c r="C48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1">
       <c r="A49">
         <v>41</v>
       </c>
@@ -4742,13 +4778,13 @@
         <v>45613</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1">
       <c r="A50">
         <v>42</v>
       </c>
@@ -4756,13 +4792,13 @@
         <v>45613</v>
       </c>
       <c r="C50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1">
       <c r="A51">
         <v>43</v>
       </c>
@@ -4770,13 +4806,13 @@
         <v>45613</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1">
       <c r="A52">
         <v>44</v>
       </c>
@@ -4784,13 +4820,13 @@
         <v>45613</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" hidden="1">
       <c r="A53">
         <v>45</v>
       </c>
@@ -4798,13 +4834,13 @@
         <v>45613</v>
       </c>
       <c r="C53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1">
       <c r="A54">
         <v>46</v>
       </c>
@@ -4812,13 +4848,13 @@
         <v>45613</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1">
       <c r="A55">
         <v>47</v>
       </c>
@@ -4826,13 +4862,13 @@
         <v>45613</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D55" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" hidden="1">
       <c r="A56">
         <v>48</v>
       </c>
@@ -4840,13 +4876,13 @@
         <v>45613</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1">
       <c r="A57">
         <v>49</v>
       </c>
@@ -4854,13 +4890,13 @@
         <v>45613</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" hidden="1">
       <c r="A58">
         <v>50</v>
       </c>
@@ -4868,13 +4904,13 @@
         <v>45613</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" hidden="1">
       <c r="A59">
         <v>51</v>
       </c>
@@ -4882,13 +4918,13 @@
         <v>45613</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" hidden="1">
       <c r="A60">
         <v>52</v>
       </c>
@@ -4896,13 +4932,13 @@
         <v>45613</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" hidden="1">
       <c r="A61">
         <v>53</v>
       </c>
@@ -4910,13 +4946,13 @@
         <v>45613</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1">
       <c r="A62">
         <v>54</v>
       </c>
@@ -4924,13 +4960,13 @@
         <v>45613</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" hidden="1">
       <c r="A63">
         <v>55</v>
       </c>
@@ -4938,13 +4974,13 @@
         <v>45613</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1">
       <c r="A64">
         <v>56</v>
       </c>
@@ -4952,13 +4988,13 @@
         <v>45613</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" hidden="1">
       <c r="A65">
         <v>57</v>
       </c>
@@ -4966,13 +5002,13 @@
         <v>45613</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" hidden="1">
       <c r="A66">
         <v>58</v>
       </c>
@@ -4980,13 +5016,13 @@
         <v>45613</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D66" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" hidden="1">
       <c r="A67">
         <v>59</v>
       </c>
@@ -4994,13 +5030,13 @@
         <v>45613</v>
       </c>
       <c r="C67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D67" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" hidden="1">
       <c r="A68">
         <v>60</v>
       </c>
@@ -5008,13 +5044,13 @@
         <v>45613</v>
       </c>
       <c r="C68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1">
       <c r="A69">
         <v>61</v>
       </c>
@@ -5022,13 +5058,13 @@
         <v>45613</v>
       </c>
       <c r="C69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" hidden="1">
       <c r="A70">
         <v>62</v>
       </c>
@@ -5036,13 +5072,13 @@
         <v>45613</v>
       </c>
       <c r="C70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D70" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" hidden="1">
       <c r="A71">
         <v>63</v>
       </c>
@@ -5050,13 +5086,13 @@
         <v>45613</v>
       </c>
       <c r="C71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1">
       <c r="A72">
         <v>64</v>
       </c>
@@ -5064,13 +5100,13 @@
         <v>45613</v>
       </c>
       <c r="C72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D72" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" hidden="1">
       <c r="A73">
         <v>65</v>
       </c>
@@ -5078,13 +5114,13 @@
         <v>45613</v>
       </c>
       <c r="C73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1">
       <c r="A74">
         <v>66</v>
       </c>
@@ -5092,13 +5128,13 @@
         <v>45613</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" hidden="1">
       <c r="A75">
         <v>67</v>
       </c>
@@ -5106,13 +5142,13 @@
         <v>45613</v>
       </c>
       <c r="C75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" hidden="1">
       <c r="A76">
         <v>68</v>
       </c>
@@ -5120,13 +5156,13 @@
         <v>45613</v>
       </c>
       <c r="C76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" hidden="1">
       <c r="A77">
         <v>69</v>
       </c>
@@ -5134,13 +5170,13 @@
         <v>45613</v>
       </c>
       <c r="C77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" hidden="1">
       <c r="A78">
         <v>70</v>
       </c>
@@ -5148,13 +5184,13 @@
         <v>45626</v>
       </c>
       <c r="C78" t="s">
+        <v>111</v>
+      </c>
+      <c r="D78" t="s">
         <v>112</v>
       </c>
-      <c r="D78" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+    </row>
+    <row r="79" spans="1:4" hidden="1">
       <c r="A79">
         <v>71</v>
       </c>
@@ -5162,13 +5198,13 @@
         <v>45626</v>
       </c>
       <c r="C79" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" t="s">
         <v>112</v>
       </c>
-      <c r="D79" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+    </row>
+    <row r="80" spans="1:4" hidden="1">
       <c r="A80">
         <v>72</v>
       </c>
@@ -5179,10 +5215,10 @@
         <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1">
       <c r="A81">
         <v>72</v>
       </c>
@@ -5190,10 +5226,10 @@
         <v>45662</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1">
       <c r="A82">
         <v>72</v>
       </c>
@@ -5201,13 +5237,13 @@
         <v>45663</v>
       </c>
       <c r="C82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E82" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1">
       <c r="A83">
         <v>73</v>
       </c>
@@ -5215,10 +5251,10 @@
         <v>45723</v>
       </c>
       <c r="C83" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" hidden="1">
       <c r="A84">
         <v>23</v>
       </c>
@@ -5226,10 +5262,10 @@
         <v>45723</v>
       </c>
       <c r="C84" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" hidden="1">
       <c r="A85">
         <v>23</v>
       </c>
@@ -5237,13 +5273,13 @@
         <v>45585</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1">
       <c r="A86">
         <v>23</v>
       </c>
@@ -5251,13 +5287,13 @@
         <v>45585</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D86" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" hidden="1">
       <c r="A87">
         <v>2</v>
       </c>
@@ -5265,10 +5301,10 @@
         <v>45723</v>
       </c>
       <c r="C87" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1">
       <c r="A88">
         <v>41</v>
       </c>
@@ -5276,10 +5312,10 @@
         <v>45723</v>
       </c>
       <c r="C88" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1">
       <c r="A89">
         <v>70</v>
       </c>
@@ -5287,13 +5323,13 @@
         <v>45725</v>
       </c>
       <c r="C89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1">
       <c r="A90">
         <v>71</v>
       </c>
@@ -5301,13 +5337,13 @@
         <v>45725</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E90" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1">
       <c r="A91">
         <v>71</v>
       </c>
@@ -5315,13 +5351,13 @@
         <v>45725</v>
       </c>
       <c r="C91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E91" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1">
       <c r="A92">
         <v>77</v>
       </c>
@@ -5329,13 +5365,13 @@
         <v>45725</v>
       </c>
       <c r="C92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E92" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1">
       <c r="A93">
         <v>75</v>
       </c>
@@ -5343,13 +5379,13 @@
         <v>45725</v>
       </c>
       <c r="C93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E93" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1">
       <c r="A94">
         <v>13</v>
       </c>
@@ -5357,13 +5393,13 @@
         <v>45725</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E94" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1">
       <c r="A95">
         <v>25</v>
       </c>
@@ -5371,13 +5407,13 @@
         <v>45725</v>
       </c>
       <c r="C95" t="s">
+        <v>152</v>
+      </c>
+      <c r="D95" t="s">
         <v>153</v>
       </c>
-      <c r="D95" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+    </row>
+    <row r="96" spans="1:5" hidden="1">
       <c r="A96">
         <v>26</v>
       </c>
@@ -5385,13 +5421,13 @@
         <v>45725</v>
       </c>
       <c r="C96" t="s">
+        <v>152</v>
+      </c>
+      <c r="D96" t="s">
         <v>153</v>
       </c>
-      <c r="D96" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+    </row>
+    <row r="97" spans="1:5" hidden="1">
       <c r="A97">
         <v>28</v>
       </c>
@@ -5399,13 +5435,13 @@
         <v>45725</v>
       </c>
       <c r="C97" t="s">
+        <v>152</v>
+      </c>
+      <c r="D97" t="s">
         <v>153</v>
       </c>
-      <c r="D97" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+    </row>
+    <row r="98" spans="1:5" hidden="1">
       <c r="A98">
         <v>27</v>
       </c>
@@ -5413,13 +5449,13 @@
         <v>45725</v>
       </c>
       <c r="C98" t="s">
+        <v>152</v>
+      </c>
+      <c r="D98" t="s">
         <v>153</v>
       </c>
-      <c r="D98" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+    </row>
+    <row r="99" spans="1:5" hidden="1">
       <c r="A99">
         <v>2</v>
       </c>
@@ -5427,13 +5463,13 @@
         <v>45725</v>
       </c>
       <c r="C99" t="s">
+        <v>152</v>
+      </c>
+      <c r="D99" t="s">
         <v>153</v>
       </c>
-      <c r="D99" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+    </row>
+    <row r="100" spans="1:5" hidden="1">
       <c r="A100">
         <v>1</v>
       </c>
@@ -5441,10 +5477,10 @@
         <v>45725</v>
       </c>
       <c r="C100" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" hidden="1">
       <c r="A101">
         <v>15</v>
       </c>
@@ -5452,10 +5488,10 @@
         <v>45731</v>
       </c>
       <c r="C101" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" hidden="1">
       <c r="A102">
         <v>10</v>
       </c>
@@ -5463,13 +5499,13 @@
         <v>44927</v>
       </c>
       <c r="C102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D102" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" hidden="1">
       <c r="A103">
         <v>74</v>
       </c>
@@ -5477,13 +5513,13 @@
         <v>45391</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E103" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" hidden="1">
       <c r="A104">
         <v>76</v>
       </c>
@@ -5491,13 +5527,13 @@
         <v>45391</v>
       </c>
       <c r="C104" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E104" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" hidden="1">
       <c r="A105">
         <v>68</v>
       </c>
@@ -5505,10 +5541,10 @@
         <v>45773</v>
       </c>
       <c r="C105" t="s">
+        <v>245</v>
+      </c>
+      <c r="E105" t="s">
         <v>246</v>
-      </c>
-      <c r="E105" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5519,13 +5555,13 @@
         <v>45788</v>
       </c>
       <c r="C106" t="s">
+        <v>258</v>
+      </c>
+      <c r="D106" t="s">
         <v>259</v>
       </c>
-      <c r="D106" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+    </row>
+    <row r="107" spans="1:5" hidden="1">
       <c r="A107">
         <v>76</v>
       </c>
@@ -5533,16 +5569,16 @@
         <v>45787</v>
       </c>
       <c r="C107" t="s">
+        <v>260</v>
+      </c>
+      <c r="D107" t="s">
         <v>261</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>262</v>
       </c>
-      <c r="E107" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+    </row>
+    <row r="108" spans="1:5" hidden="1">
       <c r="A108">
         <v>40</v>
       </c>
@@ -5550,13 +5586,13 @@
         <v>45787</v>
       </c>
       <c r="C108" t="s">
+        <v>260</v>
+      </c>
+      <c r="D108" t="s">
         <v>261</v>
       </c>
-      <c r="D108" t="s">
-        <v>262</v>
-      </c>
       <c r="E108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5567,10 +5603,10 @@
         <v>45795</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D109" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5581,13 +5617,13 @@
         <v>45805</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D110" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" hidden="1">
       <c r="A111">
         <v>40</v>
       </c>
@@ -5595,16 +5631,16 @@
         <v>45808</v>
       </c>
       <c r="C111" t="s">
+        <v>280</v>
+      </c>
+      <c r="D111" t="s">
         <v>281</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>282</v>
       </c>
-      <c r="E111" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+    </row>
+    <row r="112" spans="1:5" hidden="1">
       <c r="A112">
         <v>76</v>
       </c>
@@ -5612,16 +5648,16 @@
         <v>45808</v>
       </c>
       <c r="C112" t="s">
+        <v>280</v>
+      </c>
+      <c r="D112" t="s">
         <v>281</v>
       </c>
-      <c r="D112" t="s">
-        <v>282</v>
-      </c>
       <c r="E112" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" hidden="1">
       <c r="A113">
         <v>78</v>
       </c>
@@ -5629,16 +5665,16 @@
         <v>45830</v>
       </c>
       <c r="C113" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D113" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E113" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" hidden="1">
       <c r="A114">
         <v>79</v>
       </c>
@@ -5646,16 +5682,16 @@
         <v>45830</v>
       </c>
       <c r="C114" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D114" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E114" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" hidden="1">
       <c r="A115">
         <v>44</v>
       </c>
@@ -5663,13 +5699,13 @@
         <v>45892</v>
       </c>
       <c r="C115" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D115" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" hidden="1">
       <c r="A116">
         <v>25</v>
       </c>
@@ -5677,10 +5713,10 @@
         <v>45940</v>
       </c>
       <c r="C116" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D116" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5691,13 +5727,13 @@
         <v>45886</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D117" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" hidden="1">
       <c r="A118">
         <v>47</v>
       </c>
@@ -5705,16 +5741,73 @@
         <v>45966</v>
       </c>
       <c r="C118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D118" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E118" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" hidden="1">
+      <c r="A119">
+        <v>47</v>
+      </c>
+      <c r="B119" s="2">
+        <v>45968</v>
+      </c>
+      <c r="C119" t="s">
+        <v>92</v>
+      </c>
+      <c r="E119" t="s">
         <v>305</v>
       </c>
     </row>
+    <row r="120" spans="1:5" hidden="1">
+      <c r="A120">
+        <v>66</v>
+      </c>
+      <c r="B120" s="2">
+        <v>45976</v>
+      </c>
+      <c r="C120" t="s">
+        <v>92</v>
+      </c>
+      <c r="E120" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>82</v>
+      </c>
+      <c r="B121" s="2">
+        <v>45976</v>
+      </c>
+      <c r="C121" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>83</v>
+      </c>
+      <c r="B122" s="2">
+        <v>45976</v>
+      </c>
+      <c r="C122" t="s">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E120">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Mort"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="311">
   <si>
     <t>id</t>
   </si>
@@ -956,6 +956,9 @@
   </si>
   <si>
     <t>Arbre_66_2025-11-15_rempotage.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_71_2025-03-09_taille_rempotage.jpg</t>
   </si>
 </sst>
 </file>
@@ -1862,6 +1865,9 @@
       <c r="C21" t="s">
         <v>193</v>
       </c>
+      <c r="D21" t="s">
+        <v>179</v>
+      </c>
       <c r="F21" t="s">
         <v>111</v>
       </c>
@@ -2429,6 +2435,9 @@
     <row r="40" spans="1:20">
       <c r="A40">
         <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>179</v>
       </c>
       <c r="F40" t="s">
         <v>111</v>
@@ -3359,7 +3368,7 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="11"/>
       <c r="T71" t="s">
-        <v>148</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -3599,6 +3608,9 @@
       <c r="C80" t="s">
         <v>131</v>
       </c>
+      <c r="D80" t="s">
+        <v>179</v>
+      </c>
       <c r="F80" t="s">
         <v>132</v>
       </c>
@@ -4035,6 +4047,9 @@
       </c>
       <c r="C96" t="s">
         <v>306</v>
+      </c>
+      <c r="D96" t="s">
+        <v>179</v>
       </c>
       <c r="F96" t="s">
         <v>111</v>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -12,7 +12,7 @@
     <sheet name="actions" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">actions!$A$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">actions!$A$1:$E$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">bonsais!$A$1:$U$92</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="298">
   <si>
     <t>id</t>
   </si>
@@ -66,9 +66,6 @@
     <t>Prélèvement</t>
   </si>
   <si>
-    <t>Bouture</t>
-  </si>
-  <si>
     <t>Photo_Principale</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
     <t>Arbre_66_2024-11-17.jpeg</t>
   </si>
   <si>
-    <t>Arbre_67_2024-11-17.jpeg</t>
-  </si>
-  <si>
     <t>Arbre_68_2024-11-17.jpeg</t>
   </si>
   <si>
@@ -285,42 +279,12 @@
     <t>Engrais</t>
   </si>
   <si>
-    <t>169954507_8060ZE76.jpg</t>
-  </si>
-  <si>
-    <t>test photo</t>
-  </si>
-  <si>
-    <t>olivier_engrais.jpg</t>
-  </si>
-  <si>
-    <t>Engrais organique ajouté</t>
-  </si>
-  <si>
-    <t>erable_rempotage.jpg</t>
-  </si>
-  <si>
-    <t>Changement de pot pour un pot plus large</t>
-  </si>
-  <si>
     <t>Rempotage</t>
   </si>
   <si>
-    <t>pin_taille.jpg</t>
-  </si>
-  <si>
-    <t>Branches secondaires taillées</t>
-  </si>
-  <si>
     <t>Taille</t>
   </si>
   <si>
-    <t>pin_rempotage.jpg</t>
-  </si>
-  <si>
-    <t>Substrat akadama et pumice</t>
-  </si>
-  <si>
     <t>photo</t>
   </si>
   <si>
@@ -343,15 +307,6 @@
   </si>
   <si>
     <t>Liste de tous les bonsais</t>
-  </si>
-  <si>
-    <t>bouture transmise</t>
-  </si>
-  <si>
-    <t>24/34/98</t>
-  </si>
-  <si>
-    <t>Semence</t>
   </si>
   <si>
     <t>Aubépine</t>
@@ -931,9 +886,6 @@
     <t>Paris Bonsai Expo 2025</t>
   </si>
   <si>
-    <t>Arbre_94_2025-11-07.jpg</t>
-  </si>
-  <si>
     <t>Serissa Japonica</t>
   </si>
   <si>
@@ -959,6 +911,15 @@
   </si>
   <si>
     <t>Arbre_71_2025-03-09_taille_rempotage.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_94_2025-11-22_rempotage.jpg</t>
+  </si>
+  <si>
+    <t>Taile</t>
+  </si>
+  <si>
+    <t>Arbre_67_2025-11-22_taille.jpg</t>
   </si>
 </sst>
 </file>
@@ -988,7 +949,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -998,12 +959,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1033,14 +988,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1051,15 +1004,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1196,12 +1149,12 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1176,7 @@
     <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="24.33203125" style="2" customWidth="1"/>
     <col min="9" max="9" width="24.33203125" customWidth="1"/>
-    <col min="10" max="13" width="24.33203125" style="9" customWidth="1"/>
+    <col min="10" max="13" width="24.33203125" style="7" customWidth="1"/>
     <col min="14" max="15" width="16.6640625" customWidth="1"/>
     <col min="16" max="17" width="16.6640625" style="4" customWidth="1"/>
     <col min="18" max="18" width="28.44140625" customWidth="1"/>
@@ -1251,37 +1204,37 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="K1" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="16" t="s">
-        <v>138</v>
+      <c r="Q1" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>4</v>
@@ -1290,429 +1243,429 @@
         <v>5</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="8" customFormat="1">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" s="15">
+        <v>44982</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="T2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="10" customFormat="1">
-      <c r="A2" s="10">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" s="17">
-        <v>44982</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="T2" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" s="10" customFormat="1">
-      <c r="A3" s="10">
+    <row r="3" spans="1:20" s="8" customFormat="1">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="17">
+      <c r="C3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H3" s="15">
         <v>45591</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="T3" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" s="10" customFormat="1">
-      <c r="A4" s="10">
+      <c r="I3" s="9"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="T3" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" s="8" customFormat="1">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="17">
+      <c r="D4" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="15">
         <v>45041</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="T4" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="10" customFormat="1">
-      <c r="A5" s="10">
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="T4" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="8" customFormat="1">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="17">
+      <c r="C5" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="15">
         <v>45339</v>
       </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="S5" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="T5" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" s="10" customFormat="1">
-      <c r="A6" s="10">
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="S5" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="8" customFormat="1">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="17"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="T6" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" s="10" customFormat="1">
-      <c r="A7" s="10">
+      <c r="C6" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="T6" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="8" customFormat="1">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="17">
+      <c r="C7" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="15">
         <v>45200</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="10">
         <v>30</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="T7" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" s="10" customFormat="1">
-      <c r="A8" s="10">
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="T7" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="8" customFormat="1">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="17">
+      <c r="C8" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="15">
         <v>44835</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="T8" s="10" t="s">
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="T8" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="8" customFormat="1">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="15">
+        <v>45041</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="T9" s="8" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" s="10" customFormat="1">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="H9" s="17">
-        <v>45041</v>
-      </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="T9" s="10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="H10" s="2">
         <v>44842</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
       <c r="T10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>161</v>
+      <c r="C11" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
+        <v>166</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
       <c r="R11">
         <v>2011</v>
       </c>
       <c r="T11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="C12" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
       <c r="R12">
         <v>2024</v>
       </c>
       <c r="S12" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="T12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="C13" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
       <c r="R13">
         <v>2023</v>
       </c>
       <c r="T13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>161</v>
+      <c r="C14" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
+        <v>169</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
       <c r="R14">
         <v>2024</v>
       </c>
       <c r="T14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>161</v>
+      <c r="C15" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>187</v>
+        <v>171</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="H15" s="2">
         <v>45535</v>
       </c>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
       <c r="T15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="66">
@@ -1720,36 +1673,36 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G16" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="H16" s="2">
         <v>45591</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="7">
         <v>320</v>
       </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="14" t="s">
-        <v>164</v>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="T16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1757,30 +1710,30 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="9">
+        <v>174</v>
+      </c>
+      <c r="J17" s="7">
         <v>10</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
       <c r="R17">
         <v>2023</v>
       </c>
       <c r="T17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1788,30 +1741,30 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H18" s="2">
         <v>45261</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <v>10</v>
       </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="18">
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="16">
         <v>45261</v>
       </c>
       <c r="T18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1819,18 +1772,18 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
-      </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
+        <v>96</v>
+      </c>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
       <c r="T19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1838,24 +1791,24 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G20" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H20" s="2">
         <v>44982</v>
       </c>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
       <c r="T20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -1863,24 +1816,24 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
         <v>179</v>
       </c>
-      <c r="F21" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" t="s">
-        <v>194</v>
-      </c>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
       <c r="T21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1888,21 +1841,21 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
-      </c>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
+        <v>170</v>
+      </c>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
       <c r="T22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -1910,30 +1863,30 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F23" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>195</v>
-      </c>
-      <c r="J23" s="9">
+        <v>180</v>
+      </c>
+      <c r="J23" s="7">
         <v>50</v>
       </c>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="19">
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="17">
         <v>-0.5</v>
       </c>
       <c r="S23" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="T23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -1941,30 +1894,30 @@
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F24" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H24" s="2">
         <v>45339</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="7">
         <v>100</v>
       </c>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
       <c r="T24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -1972,24 +1925,24 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>198</v>
-      </c>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
+        <v>183</v>
+      </c>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
       <c r="R25">
         <v>2023</v>
       </c>
       <c r="T25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -1997,33 +1950,33 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="H26" s="2">
         <v>45584</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="7">
         <v>65</v>
       </c>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
       <c r="R26" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="T26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2031,33 +1984,33 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="H27" s="2">
         <v>45584</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="7">
         <v>50</v>
       </c>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
       <c r="R27" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="T27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2065,30 +2018,30 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="H28" s="2">
         <v>45413</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="7">
         <v>100</v>
       </c>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
       <c r="R28" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="T28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2096,33 +2049,33 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="H29" s="2">
         <v>45420</v>
       </c>
       <c r="I29" t="s">
-        <v>202</v>
-      </c>
-      <c r="J29" s="9">
+        <v>187</v>
+      </c>
+      <c r="J29" s="7">
         <v>100</v>
       </c>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
       <c r="T29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2130,33 +2083,33 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H30" s="2">
         <v>44982</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="7">
         <v>10</v>
       </c>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
       <c r="S30" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="T30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -2164,30 +2117,30 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G31" t="s">
-        <v>207</v>
-      </c>
-      <c r="J31" s="9">
+        <v>192</v>
+      </c>
+      <c r="J31" s="7">
         <v>30</v>
       </c>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
       <c r="R31">
         <v>2023</v>
       </c>
       <c r="T31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2195,39 +2148,39 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="E32" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H32" s="2">
         <v>45339</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="7">
         <v>18</v>
       </c>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
       <c r="R32" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="S32" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="T32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -2235,39 +2188,39 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D33" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="E33" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H33" s="2">
         <v>45339</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="7">
         <v>18</v>
       </c>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
       <c r="R33" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="S33" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="T33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -2275,24 +2228,24 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="F34" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G34" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="H34" s="2">
         <v>44896</v>
       </c>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
       <c r="T34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2300,27 +2253,27 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H35" s="2">
         <v>45339</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="7">
         <v>10</v>
       </c>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
       <c r="T35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2328,27 +2281,27 @@
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H36" s="2">
         <v>44982</v>
       </c>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
       <c r="S36" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="T36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -2356,27 +2309,27 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G37" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H37" s="2">
         <v>45200</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="7">
         <v>30</v>
       </c>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
       <c r="T37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -2384,24 +2337,24 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F38" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>217</v>
-      </c>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
+        <v>202</v>
+      </c>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
       <c r="R38">
         <v>2010</v>
       </c>
       <c r="T38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -2409,27 +2362,27 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F39" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H39" s="2">
         <v>44982</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="7">
         <v>40</v>
       </c>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
       <c r="T39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -2437,27 +2390,27 @@
         <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G40" t="s">
-        <v>200</v>
-      </c>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
+        <v>185</v>
+      </c>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
       <c r="R40" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="S40" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="T40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -2465,30 +2418,30 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="H41" s="2">
         <v>45041</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="7">
         <v>60</v>
       </c>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
       <c r="T41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -2496,27 +2449,27 @@
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G42" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="H42" s="2">
         <v>45041</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="7">
         <v>15</v>
       </c>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
       <c r="T42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -2524,27 +2477,27 @@
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G43" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="H43" s="2">
         <v>45200</v>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="7">
         <v>10</v>
       </c>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
       <c r="T43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -2552,30 +2505,30 @@
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G44" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="H44" s="2">
         <v>45200</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="7">
         <v>10</v>
       </c>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
       <c r="T44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -2583,27 +2536,27 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="F45" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G45" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="H45" s="2">
         <v>44896</v>
       </c>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
       <c r="T45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -2611,27 +2564,27 @@
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H46" s="2">
         <v>44989</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="7">
         <v>0</v>
       </c>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
       <c r="T46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -2639,27 +2592,27 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>110</v>
-      </c>
-      <c r="J47" s="9">
+        <v>95</v>
+      </c>
+      <c r="J47" s="7">
         <v>0</v>
       </c>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
       <c r="R47">
         <v>2023</v>
       </c>
       <c r="T47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -2667,27 +2620,27 @@
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H48" s="2">
         <v>45206</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="7">
         <v>0</v>
       </c>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="11"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
       <c r="T48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -2695,27 +2648,27 @@
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="F49" t="s">
-        <v>183</v>
-      </c>
-      <c r="J49" s="9">
+        <v>168</v>
+      </c>
+      <c r="J49" s="7">
         <v>0</v>
       </c>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="11"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
       <c r="R49">
         <v>2023</v>
       </c>
       <c r="S49" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="T49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -2723,27 +2676,27 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F50" t="s">
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H50" s="2">
         <v>45206</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="7">
         <v>0</v>
       </c>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
       <c r="T50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -2751,27 +2704,27 @@
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H51" s="2">
         <v>45206</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="7">
         <v>0</v>
       </c>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9"/>
       <c r="T51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -2779,27 +2732,27 @@
         <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>183</v>
-      </c>
-      <c r="J52" s="9">
+        <v>168</v>
+      </c>
+      <c r="J52" s="7">
         <v>0</v>
       </c>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
       <c r="R52">
         <v>2023</v>
       </c>
       <c r="T52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -2807,30 +2760,30 @@
         <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H53" s="2">
         <v>45206</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="7">
         <v>0</v>
       </c>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="11"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9"/>
       <c r="T53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -2838,473 +2791,473 @@
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H54" s="2">
         <v>45971</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J54" s="7">
         <v>0</v>
       </c>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
-      <c r="Q54" s="11"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9"/>
       <c r="R54" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="T54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" s="18" customFormat="1">
+      <c r="A55" s="18">
+        <v>54</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H55" s="19">
+        <v>45207</v>
+      </c>
+      <c r="J55" s="10">
+        <v>0</v>
+      </c>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20"/>
+      <c r="R55" s="18">
+        <v>2023</v>
+      </c>
+      <c r="T55" s="18" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" s="20" customFormat="1">
-      <c r="A55" s="20">
-        <v>54</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="H55" s="21">
-        <v>45207</v>
-      </c>
-      <c r="J55" s="12">
-        <v>0</v>
-      </c>
-      <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22"/>
-      <c r="O55" s="22"/>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
-      <c r="R55" s="20">
-        <v>2023</v>
-      </c>
-      <c r="T55" s="20" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="D56" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F56" s="10" t="s">
+      <c r="D56" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H56" s="2">
         <v>45206</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J56" s="7">
         <v>0</v>
       </c>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-      <c r="Q56" s="11"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9"/>
       <c r="T56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57">
         <v>57</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>161</v>
+      <c r="C57" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="E57" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H57" s="2">
         <v>45971</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="7">
         <v>0</v>
       </c>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="11"/>
-      <c r="Q57" s="11"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="9"/>
       <c r="T57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58">
         <v>58</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>161</v>
+      <c r="C58" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H58" s="2">
         <v>45971</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J58" s="7">
         <v>0</v>
       </c>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11"/>
-      <c r="P58" s="11"/>
-      <c r="Q58" s="11"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
       <c r="T58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59">
         <v>59</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>161</v>
+      <c r="C59" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H59" s="2">
         <v>45971</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="7">
         <v>0</v>
       </c>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="11"/>
-      <c r="Q59" s="11"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+      <c r="Q59" s="9"/>
       <c r="T59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60">
         <v>60</v>
       </c>
-      <c r="D60" s="10" t="s">
-        <v>232</v>
+      <c r="D60" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H60" s="2">
         <v>45206</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="7">
         <v>0</v>
       </c>
-      <c r="M60" s="11"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="11"/>
-      <c r="P60" s="11"/>
-      <c r="Q60" s="11"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
       <c r="T60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61">
         <v>61</v>
       </c>
-      <c r="D61" s="10" t="s">
-        <v>192</v>
+      <c r="D61" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H61" s="2">
         <v>45206</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="7">
         <v>0</v>
       </c>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="11"/>
-      <c r="Q61" s="11"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
       <c r="T61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62">
         <v>62</v>
       </c>
-      <c r="D62" s="10" t="s">
-        <v>192</v>
+      <c r="D62" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H62" s="2">
         <v>45206</v>
       </c>
-      <c r="J62" s="9">
+      <c r="J62" s="7">
         <v>0</v>
       </c>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="11"/>
-      <c r="Q62" s="11"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
       <c r="T62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63">
         <v>63</v>
       </c>
-      <c r="D63" s="10" t="s">
-        <v>233</v>
+      <c r="D63" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>110</v>
-      </c>
-      <c r="J63" s="9">
+        <v>95</v>
+      </c>
+      <c r="J63" s="7">
         <v>0</v>
       </c>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="11"/>
-      <c r="P63" s="11"/>
-      <c r="Q63" s="11"/>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+      <c r="Q63" s="9"/>
       <c r="R63" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="T63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64">
         <v>64</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>179</v>
+      <c r="D64" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>110</v>
-      </c>
-      <c r="J64" s="9">
+        <v>95</v>
+      </c>
+      <c r="J64" s="7">
         <v>0</v>
       </c>
-      <c r="M64" s="11"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="11"/>
-      <c r="P64" s="11"/>
-      <c r="Q64" s="11"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+      <c r="Q64" s="9"/>
       <c r="R64" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="S64" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="T64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65">
         <v>65</v>
       </c>
-      <c r="D65" s="10" t="s">
-        <v>236</v>
+      <c r="D65" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="E65" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H65" s="2">
         <v>44989</v>
       </c>
-      <c r="J65" s="9">
+      <c r="J65" s="7">
         <v>0</v>
       </c>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="11"/>
-      <c r="Q65" s="11"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="9"/>
+      <c r="O65" s="9"/>
+      <c r="P65" s="9"/>
+      <c r="Q65" s="9"/>
       <c r="T65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:20">
       <c r="A66">
         <v>66</v>
       </c>
-      <c r="D66" s="10" t="s">
-        <v>236</v>
+      <c r="D66" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H66" s="2">
         <v>44989</v>
       </c>
-      <c r="J66" s="9">
+      <c r="J66" s="7">
         <v>0</v>
       </c>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="11"/>
-      <c r="Q66" s="11"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
       <c r="T66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67">
         <v>67</v>
       </c>
-      <c r="D67" s="10" t="s">
-        <v>236</v>
+      <c r="D67" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H67" s="2">
         <v>44989</v>
       </c>
-      <c r="J67" s="9">
+      <c r="J67" s="7">
         <v>0</v>
       </c>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="11"/>
-      <c r="P67" s="11"/>
-      <c r="Q67" s="11"/>
+      <c r="M67" s="9"/>
+      <c r="N67" s="9"/>
+      <c r="O67" s="9"/>
+      <c r="P67" s="9"/>
+      <c r="Q67" s="9"/>
       <c r="T67" t="s">
-        <v>77</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68">
         <v>68</v>
       </c>
-      <c r="D68" s="10" t="s">
-        <v>237</v>
+      <c r="D68" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H68" s="2">
         <v>44989</v>
       </c>
-      <c r="J68" s="9">
+      <c r="J68" s="7">
         <v>0</v>
       </c>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="11"/>
-      <c r="Q68" s="11"/>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
       <c r="T68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:20">
       <c r="A69">
         <v>69</v>
       </c>
-      <c r="D69" s="10" t="s">
-        <v>222</v>
+      <c r="D69" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H69" s="2">
         <v>44989</v>
       </c>
-      <c r="J69" s="9">
+      <c r="J69" s="7">
         <v>0</v>
       </c>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="11"/>
-      <c r="P69" s="11"/>
-      <c r="Q69" s="11"/>
+      <c r="M69" s="9"/>
+      <c r="N69" s="9"/>
+      <c r="O69" s="9"/>
+      <c r="P69" s="9"/>
+      <c r="Q69" s="9"/>
       <c r="T69" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -3312,31 +3265,31 @@
         <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>239</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>238</v>
+        <v>224</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="F70" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G70" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H70" s="2">
         <v>45626</v>
       </c>
       <c r="I70" s="2"/>
-      <c r="J70" s="9">
+      <c r="J70" s="7">
         <v>10</v>
       </c>
-      <c r="M70" s="11"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="11"/>
-      <c r="P70" s="11"/>
-      <c r="Q70" s="11"/>
+      <c r="M70" s="9"/>
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+      <c r="P70" s="9"/>
+      <c r="Q70" s="9"/>
       <c r="T70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -3344,60 +3297,60 @@
         <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>241</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>240</v>
+        <v>226</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="F71" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H71" s="2">
         <v>45626</v>
       </c>
       <c r="I71" s="2"/>
-      <c r="J71" s="9">
+      <c r="J71" s="7">
         <v>12</v>
       </c>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11"/>
-      <c r="P71" s="11"/>
-      <c r="Q71" s="11"/>
+      <c r="M71" s="9"/>
+      <c r="N71" s="9"/>
+      <c r="O71" s="9"/>
+      <c r="P71" s="9"/>
+      <c r="Q71" s="9"/>
       <c r="T71" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:20">
       <c r="A72">
         <v>72</v>
       </c>
-      <c r="D72" s="10" t="s">
-        <v>109</v>
+      <c r="D72" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
       </c>
       <c r="G72" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="H72" s="2">
         <v>45662</v>
       </c>
       <c r="I72" s="2"/>
-      <c r="J72" s="9">
+      <c r="J72" s="7">
         <v>0</v>
       </c>
-      <c r="M72" s="11"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="11"/>
-      <c r="P72" s="11"/>
-      <c r="Q72" s="11"/>
+      <c r="M72" s="9"/>
+      <c r="N72" s="9"/>
+      <c r="O72" s="9"/>
+      <c r="P72" s="9"/>
+      <c r="Q72" s="9"/>
       <c r="T72" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -3405,28 +3358,28 @@
         <v>73</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F73" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G73" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H73" s="2">
         <v>45675</v>
       </c>
-      <c r="I73" s="7"/>
-      <c r="J73" s="9">
+      <c r="I73" s="5"/>
+      <c r="J73" s="7">
         <v>0</v>
       </c>
-      <c r="M73" s="11"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="11"/>
-      <c r="P73" s="11"/>
-      <c r="Q73" s="11"/>
+      <c r="M73" s="9"/>
+      <c r="N73" s="9"/>
+      <c r="O73" s="9"/>
+      <c r="P73" s="9"/>
+      <c r="Q73" s="9"/>
       <c r="T73" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -3434,25 +3387,25 @@
         <v>74</v>
       </c>
       <c r="D74" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F74" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H74" s="2">
         <v>45675</v>
       </c>
-      <c r="I74" s="7"/>
-      <c r="J74" s="9">
+      <c r="I74" s="5"/>
+      <c r="J74" s="7">
         <v>10</v>
       </c>
-      <c r="M74" s="11"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="11"/>
-      <c r="P74" s="11"/>
-      <c r="Q74" s="11"/>
+      <c r="M74" s="9"/>
+      <c r="N74" s="9"/>
+      <c r="O74" s="9"/>
+      <c r="P74" s="9"/>
+      <c r="Q74" s="9"/>
       <c r="T74" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -3460,25 +3413,25 @@
         <v>75</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F75" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G75" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H75" s="2">
         <v>45675</v>
       </c>
-      <c r="I75" s="7"/>
-      <c r="J75" s="9">
+      <c r="I75" s="5"/>
+      <c r="J75" s="7">
         <v>0</v>
       </c>
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="T75" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -3486,26 +3439,26 @@
         <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F76" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G76" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H76" s="2">
         <v>45710</v>
       </c>
-      <c r="I76" s="7"/>
-      <c r="J76" s="9">
+      <c r="I76" s="5"/>
+      <c r="J76" s="7">
         <v>185</v>
       </c>
       <c r="T76" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -3513,28 +3466,28 @@
         <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F77" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G77" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H77" s="2">
         <v>45710</v>
       </c>
-      <c r="I77" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J77" s="9">
+      <c r="I77" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J77" s="7">
         <v>70</v>
       </c>
       <c r="T77" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -3542,34 +3495,34 @@
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F78" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G78" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H78" s="2">
         <v>45710</v>
       </c>
-      <c r="I78" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="J78" s="9">
+      <c r="I78" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J78" s="7">
         <v>140</v>
       </c>
       <c r="R78" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="S78" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="T78" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -3577,28 +3530,28 @@
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F79" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G79" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H79" s="2">
         <v>45710</v>
       </c>
-      <c r="I79" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J79" s="9">
+      <c r="I79" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J79" s="7">
         <v>35</v>
       </c>
       <c r="T79" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -3606,54 +3559,54 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G80" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H80" s="2">
         <v>45710</v>
       </c>
-      <c r="J80" s="9">
+      <c r="J80" s="7">
         <v>0</v>
       </c>
       <c r="R80" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="T80" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:20">
-      <c r="A81" s="23">
+      <c r="A81" s="21">
         <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D81" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="F81" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G81" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H81" s="2">
         <v>45774</v>
       </c>
-      <c r="J81" s="9">
+      <c r="J81" s="7">
         <v>20</v>
       </c>
       <c r="T81" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -3661,28 +3614,28 @@
         <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D82" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F82" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G82" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H82" s="2">
         <v>45774</v>
       </c>
-      <c r="J82" s="9">
+      <c r="J82" s="7">
         <v>0</v>
       </c>
       <c r="R82" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="T82" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -3690,28 +3643,28 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D83" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="F83" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G83" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H83" s="2">
         <v>45774</v>
       </c>
-      <c r="J83" s="9">
+      <c r="J83" s="7">
         <v>5</v>
       </c>
       <c r="R83" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="T83" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -3719,31 +3672,31 @@
         <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D84" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E84" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="F84" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H84" s="2">
         <v>45774</v>
       </c>
-      <c r="J84" s="9">
+      <c r="J84" s="7">
         <v>2</v>
       </c>
       <c r="R84" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="T84" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -3751,25 +3704,25 @@
         <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F85" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G85" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="H85" s="2">
         <v>45794</v>
       </c>
-      <c r="J85" s="9">
+      <c r="J85" s="7">
         <v>45</v>
       </c>
       <c r="R85" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="T85" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -3777,28 +3730,28 @@
         <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F86" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G86" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="H86" s="2">
         <v>45794</v>
       </c>
-      <c r="J86" s="9">
+      <c r="J86" s="7">
         <v>50</v>
       </c>
       <c r="R86" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="T86" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -3806,28 +3759,28 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F87" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G87" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="H87" s="2">
         <v>45794</v>
       </c>
-      <c r="J87" s="9">
+      <c r="J87" s="7">
         <v>70</v>
       </c>
       <c r="R87" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="T87" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -3835,28 +3788,28 @@
         <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D88" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="F88" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G88" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H88" s="2">
         <v>45809</v>
       </c>
-      <c r="J88" s="9">
+      <c r="J88" s="7">
         <v>10</v>
       </c>
       <c r="R88" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="T88" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -3864,28 +3817,28 @@
         <v>88</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F89" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G89" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H89" s="2">
         <v>45808</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J89" s="7">
         <v>40</v>
       </c>
       <c r="R89" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="T89" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -3893,25 +3846,25 @@
         <v>89</v>
       </c>
       <c r="D90" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F90" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H90" s="2">
         <v>45808</v>
       </c>
-      <c r="J90" s="9">
+      <c r="J90" s="7">
         <v>0</v>
       </c>
       <c r="R90" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="T90" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -3919,22 +3872,22 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="F91" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G91" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="H91" s="2">
         <v>45824</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J91" s="7">
         <v>3.99</v>
       </c>
       <c r="T91" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -3942,25 +3895,25 @@
         <v>91</v>
       </c>
       <c r="C92" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D92" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F92" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G92" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="H92" s="2">
         <v>45830</v>
       </c>
-      <c r="J92" s="9">
+      <c r="J92" s="7">
         <v>100</v>
       </c>
       <c r="T92" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -3968,25 +3921,25 @@
         <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D93" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F93" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G93" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H93" s="2">
         <v>45927</v>
       </c>
-      <c r="J93" s="9">
+      <c r="J93" s="7">
         <v>5</v>
       </c>
       <c r="T93" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -3994,22 +3947,22 @@
         <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G94" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="H94" s="2">
         <v>45927</v>
       </c>
-      <c r="J94" s="9">
+      <c r="J94" s="7">
         <v>10</v>
       </c>
       <c r="T94" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -4017,28 +3970,28 @@
         <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="D95" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="F95" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G95" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="H95" s="2">
         <v>45962</v>
       </c>
-      <c r="J95" s="9">
+      <c r="J95" s="7">
         <v>25</v>
       </c>
       <c r="R95" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="T95" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -4046,25 +3999,25 @@
         <v>95</v>
       </c>
       <c r="C96" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D96" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F96" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G96" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="H96" s="2">
         <v>45976</v>
       </c>
-      <c r="J96" s="9">
+      <c r="J96" s="7">
         <v>9.99</v>
       </c>
       <c r="T96" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4085,10 +4038,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -4100,1728 +4053,1653 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>101</v>
+        <v>90</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A2" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>45364</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C46" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C48" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C49" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C50" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C54" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C56" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C57" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C59" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C60" t="s">
+        <v>83</v>
+      </c>
+      <c r="D60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C62" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C63" t="s">
+        <v>83</v>
+      </c>
+      <c r="D63" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C64" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C66" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C67" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C68" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C69" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C70" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C72" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6">
-        <v>45458</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D72" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>45662</v>
+      </c>
+      <c r="C73" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6">
-        <v>45189</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6">
-        <v>45620</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A6" s="5">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6">
-        <v>45624</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A7" s="5">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6">
-        <v>12776</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="5" customFormat="1" hidden="1">
-      <c r="A8" s="5">
-        <v>1</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" hidden="1">
-      <c r="A13">
-        <v>5</v>
-      </c>
-      <c r="B13" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" hidden="1">
-      <c r="A14">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" hidden="1">
-      <c r="A15">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" hidden="1">
-      <c r="A16">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1">
-      <c r="A17">
-        <v>9</v>
-      </c>
-      <c r="B17" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" hidden="1">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1">
-      <c r="A19">
-        <v>11</v>
-      </c>
-      <c r="B19" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1">
-      <c r="A20">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1">
-      <c r="A21">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1">
-      <c r="A22">
-        <v>14</v>
-      </c>
-      <c r="B22" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" hidden="1">
-      <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="B23" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1">
-      <c r="A24">
-        <v>16</v>
-      </c>
-      <c r="B24" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1">
-      <c r="A25">
-        <v>17</v>
-      </c>
-      <c r="B25" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" hidden="1">
-      <c r="A26">
-        <v>18</v>
-      </c>
-      <c r="B26" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" hidden="1">
-      <c r="A27">
-        <v>19</v>
-      </c>
-      <c r="B27" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" hidden="1">
-      <c r="A28">
-        <v>20</v>
-      </c>
-      <c r="B28" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" hidden="1">
-      <c r="A29">
-        <v>21</v>
-      </c>
-      <c r="B29" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" hidden="1">
-      <c r="A30">
-        <v>22</v>
-      </c>
-      <c r="B30" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" hidden="1">
-      <c r="A31">
-        <v>23</v>
-      </c>
-      <c r="B31" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" hidden="1">
-      <c r="A32">
-        <v>24</v>
-      </c>
-      <c r="B32" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1">
-      <c r="A33">
-        <v>25</v>
-      </c>
-      <c r="B33" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1">
-      <c r="A34">
-        <v>26</v>
-      </c>
-      <c r="B34" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C34" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1">
-      <c r="A35">
-        <v>27</v>
-      </c>
-      <c r="B35" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C35" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1">
-      <c r="A36">
-        <v>28</v>
-      </c>
-      <c r="B36" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C36" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1">
-      <c r="A37">
-        <v>29</v>
-      </c>
-      <c r="B37" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C37" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1">
-      <c r="A38">
-        <v>30</v>
-      </c>
-      <c r="B38" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C38" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1">
-      <c r="A39">
-        <v>31</v>
-      </c>
-      <c r="B39" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1">
-      <c r="A40">
-        <v>32</v>
-      </c>
-      <c r="B40" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" hidden="1">
-      <c r="A41">
-        <v>33</v>
-      </c>
-      <c r="B41" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" hidden="1">
-      <c r="A42">
-        <v>34</v>
-      </c>
-      <c r="B42" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" hidden="1">
-      <c r="A43">
-        <v>35</v>
-      </c>
-      <c r="B43" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1">
-      <c r="A44">
-        <v>36</v>
-      </c>
-      <c r="B44" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" hidden="1">
-      <c r="A45">
-        <v>37</v>
-      </c>
-      <c r="B45" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1">
-      <c r="A46">
-        <v>38</v>
-      </c>
-      <c r="B46" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C46" t="s">
-        <v>85</v>
-      </c>
-      <c r="D46" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1">
-      <c r="A47">
-        <v>39</v>
-      </c>
-      <c r="B47" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C47" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" hidden="1">
-      <c r="A48">
-        <v>40</v>
-      </c>
-      <c r="B48" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C48" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" hidden="1">
-      <c r="A49">
-        <v>41</v>
-      </c>
-      <c r="B49" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C49" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" hidden="1">
-      <c r="A50">
-        <v>42</v>
-      </c>
-      <c r="B50" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C50" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" hidden="1">
-      <c r="A51">
-        <v>43</v>
-      </c>
-      <c r="B51" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" hidden="1">
-      <c r="A52">
-        <v>44</v>
-      </c>
-      <c r="B52" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C52" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" hidden="1">
-      <c r="A53">
-        <v>45</v>
-      </c>
-      <c r="B53" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C53" t="s">
-        <v>85</v>
-      </c>
-      <c r="D53" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" hidden="1">
-      <c r="A54">
-        <v>46</v>
-      </c>
-      <c r="B54" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C54" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" hidden="1">
-      <c r="A55">
-        <v>47</v>
-      </c>
-      <c r="B55" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C55" t="s">
-        <v>85</v>
-      </c>
-      <c r="D55" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" hidden="1">
-      <c r="A56">
-        <v>48</v>
-      </c>
-      <c r="B56" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C56" t="s">
-        <v>85</v>
-      </c>
-      <c r="D56" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" hidden="1">
-      <c r="A57">
-        <v>49</v>
-      </c>
-      <c r="B57" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C57" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" hidden="1">
-      <c r="A58">
-        <v>50</v>
-      </c>
-      <c r="B58" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C58" t="s">
-        <v>85</v>
-      </c>
-      <c r="D58" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" hidden="1">
-      <c r="A59">
-        <v>51</v>
-      </c>
-      <c r="B59" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C59" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" hidden="1">
-      <c r="A60">
-        <v>52</v>
-      </c>
-      <c r="B60" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C60" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" hidden="1">
-      <c r="A61">
-        <v>53</v>
-      </c>
-      <c r="B61" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C61" t="s">
-        <v>85</v>
-      </c>
-      <c r="D61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" hidden="1">
-      <c r="A62">
-        <v>54</v>
-      </c>
-      <c r="B62" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C62" t="s">
-        <v>85</v>
-      </c>
-      <c r="D62" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" hidden="1">
-      <c r="A63">
-        <v>55</v>
-      </c>
-      <c r="B63" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C63" t="s">
-        <v>85</v>
-      </c>
-      <c r="D63" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" hidden="1">
-      <c r="A64">
-        <v>56</v>
-      </c>
-      <c r="B64" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C64" t="s">
-        <v>85</v>
-      </c>
-      <c r="D64" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" hidden="1">
-      <c r="A65">
-        <v>57</v>
-      </c>
-      <c r="B65" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C65" t="s">
-        <v>85</v>
-      </c>
-      <c r="D65" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" hidden="1">
-      <c r="A66">
-        <v>58</v>
-      </c>
-      <c r="B66" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C66" t="s">
-        <v>85</v>
-      </c>
-      <c r="D66" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" hidden="1">
-      <c r="A67">
-        <v>59</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C67" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" hidden="1">
-      <c r="A68">
-        <v>60</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C68" t="s">
-        <v>85</v>
-      </c>
-      <c r="D68" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" hidden="1">
-      <c r="A69">
-        <v>61</v>
-      </c>
-      <c r="B69" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C69" t="s">
-        <v>85</v>
-      </c>
-      <c r="D69" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" hidden="1">
-      <c r="A70">
-        <v>62</v>
-      </c>
-      <c r="B70" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C70" t="s">
-        <v>85</v>
-      </c>
-      <c r="D70" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" hidden="1">
-      <c r="A71">
-        <v>63</v>
-      </c>
-      <c r="B71" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C71" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" hidden="1">
-      <c r="A72">
-        <v>64</v>
-      </c>
-      <c r="B72" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C72" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" hidden="1">
-      <c r="A73">
-        <v>65</v>
-      </c>
-      <c r="B73" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C73" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" hidden="1">
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>45613</v>
+        <v>45662</v>
       </c>
       <c r="C74" t="s">
         <v>85</v>
       </c>
-      <c r="D74" t="s">
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75" s="2">
+        <v>45663</v>
+      </c>
+      <c r="C75" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76" s="2">
+        <v>45723</v>
+      </c>
+      <c r="C76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>23</v>
+      </c>
+      <c r="B77" s="2">
+        <v>45723</v>
+      </c>
+      <c r="C77" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>23</v>
+      </c>
+      <c r="B78" s="2">
+        <v>45585</v>
+      </c>
+      <c r="C78" t="s">
+        <v>118</v>
+      </c>
+      <c r="D78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>23</v>
+      </c>
+      <c r="B79" s="2">
+        <v>45585</v>
+      </c>
+      <c r="C79" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" hidden="1">
-      <c r="A75">
-        <v>67</v>
-      </c>
-      <c r="B75" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="D79" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>2</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45723</v>
+      </c>
+      <c r="C80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>41</v>
+      </c>
+      <c r="B81" s="2">
+        <v>45723</v>
+      </c>
+      <c r="C81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>70</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45725</v>
+      </c>
+      <c r="C82" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>71</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45725</v>
+      </c>
+      <c r="C83" t="s">
         <v>85</v>
       </c>
-      <c r="D75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" hidden="1">
-      <c r="A76">
-        <v>68</v>
-      </c>
-      <c r="B76" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C76" t="s">
-        <v>85</v>
-      </c>
-      <c r="D76" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" hidden="1">
-      <c r="A77">
-        <v>69</v>
-      </c>
-      <c r="B77" s="2">
-        <v>45613</v>
-      </c>
-      <c r="C77" t="s">
-        <v>85</v>
-      </c>
-      <c r="D77" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" hidden="1">
-      <c r="A78">
-        <v>70</v>
-      </c>
-      <c r="B78" s="2">
-        <v>45626</v>
-      </c>
-      <c r="C78" t="s">
-        <v>111</v>
-      </c>
-      <c r="D78" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" hidden="1">
-      <c r="A79">
+      <c r="E83" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
         <v>71</v>
       </c>
-      <c r="B79" s="2">
-        <v>45626</v>
-      </c>
-      <c r="C79" t="s">
-        <v>111</v>
-      </c>
-      <c r="D79" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" hidden="1">
-      <c r="A80">
-        <v>72</v>
-      </c>
-      <c r="B80" s="2">
-        <v>45662</v>
-      </c>
-      <c r="C80" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" hidden="1">
-      <c r="A81">
-        <v>72</v>
-      </c>
-      <c r="B81" s="2">
-        <v>45662</v>
-      </c>
-      <c r="C81" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" hidden="1">
-      <c r="A82">
-        <v>72</v>
-      </c>
-      <c r="B82" s="2">
-        <v>45663</v>
-      </c>
-      <c r="C82" t="s">
-        <v>92</v>
-      </c>
-      <c r="E82" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" hidden="1">
-      <c r="A83">
-        <v>73</v>
-      </c>
-      <c r="B83" s="2">
-        <v>45723</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="B84" s="2">
+        <v>45725</v>
+      </c>
+      <c r="C84" t="s">
+        <v>84</v>
+      </c>
+      <c r="E84" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1">
-      <c r="A84">
-        <v>23</v>
-      </c>
-      <c r="B84" s="2">
-        <v>45723</v>
-      </c>
-      <c r="C84" t="s">
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>77</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45725</v>
+      </c>
+      <c r="C85" t="s">
+        <v>84</v>
+      </c>
+      <c r="E85" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1">
-      <c r="A85">
-        <v>23</v>
-      </c>
-      <c r="B85" s="2">
-        <v>45585</v>
-      </c>
-      <c r="C85" t="s">
-        <v>133</v>
-      </c>
-      <c r="D85" t="s">
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>75</v>
+      </c>
+      <c r="B86" s="2">
+        <v>45725</v>
+      </c>
+      <c r="C86" t="s">
+        <v>84</v>
+      </c>
+      <c r="E86" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1">
-      <c r="A86">
-        <v>23</v>
-      </c>
-      <c r="B86" s="2">
-        <v>45585</v>
-      </c>
-      <c r="C86" t="s">
-        <v>95</v>
-      </c>
-      <c r="D86" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" hidden="1">
+    <row r="87" spans="1:5">
       <c r="A87">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B87" s="2">
-        <v>45723</v>
+        <v>45725</v>
       </c>
       <c r="C87" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" hidden="1">
+        <v>84</v>
+      </c>
+      <c r="E87" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B88" s="2">
-        <v>45723</v>
+        <v>45725</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1">
+        <v>137</v>
+      </c>
+      <c r="D88" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="B89" s="2">
         <v>45725</v>
       </c>
       <c r="C89" t="s">
-        <v>92</v>
-      </c>
-      <c r="E89" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1">
+        <v>137</v>
+      </c>
+      <c r="D89" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B90" s="2">
         <v>45725</v>
       </c>
       <c r="C90" t="s">
-        <v>95</v>
-      </c>
-      <c r="E90" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1">
+        <v>137</v>
+      </c>
+      <c r="D90" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="B91" s="2">
         <v>45725</v>
       </c>
       <c r="C91" t="s">
-        <v>92</v>
-      </c>
-      <c r="E91" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" hidden="1">
+        <v>137</v>
+      </c>
+      <c r="D91" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="B92" s="2">
         <v>45725</v>
       </c>
       <c r="C92" t="s">
-        <v>92</v>
-      </c>
-      <c r="E92" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" hidden="1">
+        <v>137</v>
+      </c>
+      <c r="D92" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="B93" s="2">
         <v>45725</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
-      </c>
-      <c r="E93" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" hidden="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B94" s="2">
-        <v>45725</v>
+        <v>45731</v>
       </c>
       <c r="C94" t="s">
-        <v>92</v>
-      </c>
-      <c r="E94" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" hidden="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B95" s="2">
-        <v>45725</v>
+        <v>44927</v>
       </c>
       <c r="C95" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="D95" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" hidden="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="B96" s="2">
-        <v>45725</v>
+        <v>45391</v>
       </c>
       <c r="C96" t="s">
-        <v>152</v>
-      </c>
-      <c r="D96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" hidden="1">
+        <v>119</v>
+      </c>
+      <c r="E96" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="B97" s="2">
-        <v>45725</v>
+        <v>45391</v>
       </c>
       <c r="C97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D97" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" hidden="1">
+        <v>119</v>
+      </c>
+      <c r="E97" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B98" s="2">
-        <v>45725</v>
+        <v>45773</v>
       </c>
       <c r="C98" t="s">
-        <v>152</v>
-      </c>
-      <c r="D98" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" hidden="1">
+        <v>230</v>
+      </c>
+      <c r="E98" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B99" s="2">
-        <v>45725</v>
+        <v>45788</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="D99" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" hidden="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="B100" s="2">
-        <v>45725</v>
+        <v>45787</v>
       </c>
       <c r="C100" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" hidden="1">
+        <v>245</v>
+      </c>
+      <c r="D100" t="s">
+        <v>246</v>
+      </c>
+      <c r="E100" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B101" s="2">
-        <v>45731</v>
+        <v>45787</v>
       </c>
       <c r="C101" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" hidden="1">
+        <v>245</v>
+      </c>
+      <c r="D101" t="s">
+        <v>246</v>
+      </c>
+      <c r="E101" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B102" s="2">
-        <v>44927</v>
+        <v>45795</v>
       </c>
       <c r="C102" t="s">
-        <v>95</v>
+        <v>243</v>
       </c>
       <c r="D102" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" hidden="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B103" s="2">
-        <v>45391</v>
+        <v>45805</v>
       </c>
       <c r="C103" t="s">
-        <v>134</v>
-      </c>
-      <c r="E103" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" hidden="1">
+      <c r="D103" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104">
+        <v>40</v>
+      </c>
+      <c r="B104" s="2">
+        <v>45808</v>
+      </c>
+      <c r="C104" t="s">
+        <v>265</v>
+      </c>
+      <c r="D104" t="s">
+        <v>266</v>
+      </c>
+      <c r="E104" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
         <v>76</v>
       </c>
-      <c r="B104" s="2">
-        <v>45391</v>
-      </c>
-      <c r="C104" t="s">
-        <v>134</v>
-      </c>
-      <c r="E104" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" hidden="1">
-      <c r="A105">
-        <v>68</v>
-      </c>
       <c r="B105" s="2">
-        <v>45773</v>
+        <v>45808</v>
       </c>
       <c r="C105" t="s">
-        <v>245</v>
+        <v>265</v>
+      </c>
+      <c r="D105" t="s">
+        <v>266</v>
       </c>
       <c r="E105" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B106" s="2">
-        <v>45788</v>
+        <v>45830</v>
       </c>
       <c r="C106" t="s">
-        <v>258</v>
+        <v>85</v>
       </c>
       <c r="D106" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" hidden="1">
+        <v>275</v>
+      </c>
+      <c r="E106" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B107" s="2">
-        <v>45787</v>
+        <v>45830</v>
       </c>
       <c r="C107" t="s">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="D107" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="E107" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" hidden="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B108" s="2">
-        <v>45787</v>
+        <v>45892</v>
       </c>
       <c r="C108" t="s">
-        <v>260</v>
+        <v>118</v>
       </c>
       <c r="D108" t="s">
-        <v>261</v>
-      </c>
-      <c r="E108" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B109" s="2">
-        <v>45795</v>
+        <v>45940</v>
       </c>
       <c r="C109" t="s">
-        <v>258</v>
+        <v>85</v>
       </c>
       <c r="D109" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B110" s="2">
-        <v>45805</v>
+        <v>45886</v>
       </c>
       <c r="C110" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D110" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" hidden="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B111" s="2">
-        <v>45808</v>
+        <v>45966</v>
       </c>
       <c r="C111" t="s">
-        <v>280</v>
+        <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E111" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" hidden="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="B112" s="2">
-        <v>45808</v>
+        <v>45968</v>
       </c>
       <c r="C112" t="s">
-        <v>280</v>
-      </c>
-      <c r="D112" t="s">
-        <v>281</v>
+        <v>84</v>
       </c>
       <c r="E112" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" hidden="1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B113" s="2">
-        <v>45830</v>
+        <v>45976</v>
       </c>
       <c r="C113" t="s">
-        <v>95</v>
-      </c>
-      <c r="D113" t="s">
-        <v>290</v>
+        <v>84</v>
       </c>
       <c r="E113" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B114" s="2">
-        <v>45830</v>
+        <v>45976</v>
       </c>
       <c r="C114" t="s">
-        <v>95</v>
-      </c>
-      <c r="D114" t="s">
-        <v>290</v>
-      </c>
-      <c r="E114" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" hidden="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="B115" s="2">
-        <v>45892</v>
+        <v>45976</v>
       </c>
       <c r="C115" t="s">
-        <v>133</v>
-      </c>
-      <c r="D115" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" hidden="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B116" s="2">
-        <v>45940</v>
+        <v>45983</v>
       </c>
       <c r="C116" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D116" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B117" s="2">
-        <v>45886</v>
+        <v>45983</v>
       </c>
       <c r="C117" t="s">
-        <v>258</v>
-      </c>
-      <c r="D117" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" hidden="1">
+        <v>84</v>
+      </c>
+      <c r="E117" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B118" s="2">
-        <v>45966</v>
+        <v>45983</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
-      </c>
-      <c r="D118" t="s">
-        <v>292</v>
-      </c>
-      <c r="E118" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" hidden="1">
-      <c r="A119">
-        <v>47</v>
-      </c>
-      <c r="B119" s="2">
-        <v>45968</v>
-      </c>
-      <c r="C119" t="s">
-        <v>92</v>
-      </c>
-      <c r="E119" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" hidden="1">
-      <c r="A120">
-        <v>66</v>
-      </c>
-      <c r="B120" s="2">
-        <v>45976</v>
-      </c>
-      <c r="C120" t="s">
-        <v>92</v>
-      </c>
-      <c r="E120" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121">
-        <v>82</v>
-      </c>
-      <c r="B121" s="2">
-        <v>45976</v>
-      </c>
-      <c r="C121" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122">
-        <v>83</v>
-      </c>
-      <c r="B122" s="2">
-        <v>45976</v>
-      </c>
-      <c r="C122" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E120">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Mort"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:E116">
+    <filterColumn colId="2"/>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">actions!$A$1:$E$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">bonsais!$A$1:$U$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">bonsais!$A$1:$U$102</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="305">
   <si>
     <t>id</t>
   </si>
@@ -625,9 +625,6 @@
     <t>Famille à confirmer</t>
   </si>
   <si>
-    <t>Conassier du Japon</t>
-  </si>
-  <si>
     <t>Joël</t>
   </si>
   <si>
@@ -898,9 +895,6 @@
     <t>Arbre_47_2025-11-07-pot.jpg</t>
   </si>
   <si>
-    <t>Callicarpa</t>
-  </si>
-  <si>
     <t>Hyper U</t>
   </si>
   <si>
@@ -920,6 +914,33 @@
   </si>
   <si>
     <t>Arbre_67_2025-11-22_taille.jpg</t>
+  </si>
+  <si>
+    <t>Pot plus petit et plus large</t>
+  </si>
+  <si>
+    <t>Chêne Liège</t>
+  </si>
+  <si>
+    <t>Nouveau pot</t>
+  </si>
+  <si>
+    <t>Arbre_96_2025-03-18.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_97_2025-03-18.jpg</t>
+  </si>
+  <si>
+    <t>Callicarpa Japonica</t>
+  </si>
+  <si>
+    <t>Arbre_98_2025-03-18.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_99_2025-03-18.jpg</t>
+  </si>
+  <si>
+    <t>Cognassier du Japon</t>
   </si>
 </sst>
 </file>
@@ -1167,10 +1188,10 @@
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.21875" customWidth="1"/>
     <col min="3" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
@@ -1216,10 +1237,10 @@
         <v>107</v>
       </c>
       <c r="K1" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="L1" s="13" t="s">
         <v>248</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>249</v>
       </c>
       <c r="M1" s="13" t="s">
         <v>122</v>
@@ -2148,7 +2169,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
         <v>189</v>
@@ -2188,7 +2209,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
         <v>189</v>
@@ -2253,7 +2274,7 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F35" t="s">
         <v>96</v>
@@ -2309,13 +2330,13 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="F37" t="s">
         <v>99</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H37" s="2">
         <v>45200</v>
@@ -2337,13 +2358,13 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" t="s">
         <v>201</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" t="s">
-        <v>202</v>
       </c>
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
@@ -2362,7 +2383,7 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F39" t="s">
         <v>96</v>
@@ -2404,7 +2425,7 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S40" t="s">
         <v>198</v>
@@ -2483,7 +2504,7 @@
         <v>99</v>
       </c>
       <c r="G43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H43" s="2">
         <v>45200</v>
@@ -2508,13 +2529,13 @@
         <v>182</v>
       </c>
       <c r="E44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F44" t="s">
         <v>99</v>
       </c>
       <c r="G44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H44" s="2">
         <v>45200</v>
@@ -2536,10 +2557,10 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F45" t="s">
         <v>117</v>
@@ -2564,13 +2585,13 @@
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H46" s="2">
         <v>44989</v>
@@ -2592,7 +2613,7 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -2620,13 +2641,13 @@
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H48" s="2">
         <v>45206</v>
@@ -2648,7 +2669,7 @@
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F49" t="s">
         <v>168</v>
@@ -2665,7 +2686,7 @@
         <v>2023</v>
       </c>
       <c r="S49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="T49" t="s">
         <v>56</v>
@@ -2682,7 +2703,7 @@
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H50" s="2">
         <v>45206</v>
@@ -2710,7 +2731,7 @@
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H51" s="2">
         <v>45206</v>
@@ -2732,7 +2753,7 @@
         <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E52" t="s">
         <v>171</v>
@@ -2760,7 +2781,7 @@
         <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E53" t="s">
         <v>171</v>
@@ -2769,7 +2790,7 @@
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H53" s="2">
         <v>45206</v>
@@ -2791,13 +2812,13 @@
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H54" s="2">
         <v>45971</v>
@@ -2811,7 +2832,7 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="R54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T54" t="s">
         <v>62</v>
@@ -2828,7 +2849,7 @@
         <v>117</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H55" s="19">
         <v>45207</v>
@@ -2855,13 +2876,13 @@
         <v>55</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H56" s="2">
         <v>45206</v>
@@ -2895,7 +2916,7 @@
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H57" s="2">
         <v>45971</v>
@@ -2926,7 +2947,7 @@
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H58" s="2">
         <v>45971</v>
@@ -2957,7 +2978,7 @@
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H59" s="2">
         <v>45971</v>
@@ -2979,13 +3000,13 @@
         <v>60</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H60" s="2">
         <v>45206</v>
@@ -3013,7 +3034,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H61" s="2">
         <v>45206</v>
@@ -3041,7 +3062,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H62" s="2">
         <v>45206</v>
@@ -3063,7 +3084,7 @@
         <v>63</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -3080,7 +3101,7 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
       <c r="R63" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="T63" t="s">
         <v>72</v>
@@ -3108,10 +3129,10 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
       <c r="R64" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S64" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T64" t="s">
         <v>73</v>
@@ -3122,7 +3143,7 @@
         <v>65</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
@@ -3131,7 +3152,7 @@
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H65" s="2">
         <v>44989</v>
@@ -3153,13 +3174,13 @@
         <v>66</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H66" s="2">
         <v>44989</v>
@@ -3181,13 +3202,13 @@
         <v>67</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H67" s="2">
         <v>44989</v>
@@ -3201,7 +3222,7 @@
       <c r="P67" s="9"/>
       <c r="Q67" s="9"/>
       <c r="T67" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -3209,13 +3230,13 @@
         <v>68</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H68" s="2">
         <v>44989</v>
@@ -3237,13 +3258,13 @@
         <v>69</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H69" s="2">
         <v>44989</v>
@@ -3265,10 +3286,10 @@
         <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F70" t="s">
         <v>96</v>
@@ -3297,10 +3318,10 @@
         <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F71" t="s">
         <v>96</v>
@@ -3321,7 +3342,7 @@
       <c r="P71" s="9"/>
       <c r="Q71" s="9"/>
       <c r="T71" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -3405,7 +3426,7 @@
       <c r="P74" s="9"/>
       <c r="Q74" s="9"/>
       <c r="T74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -3577,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T80" t="s">
         <v>144</v>
@@ -3588,16 +3609,16 @@
         <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D81" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F81" t="s">
         <v>96</v>
       </c>
       <c r="G81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H81" s="2">
         <v>45774</v>
@@ -3606,7 +3627,7 @@
         <v>20</v>
       </c>
       <c r="T81" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -3614,16 +3635,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F82" t="s">
         <v>117</v>
       </c>
       <c r="G82" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H82" s="2">
         <v>45774</v>
@@ -3632,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="R82" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -3643,16 +3664,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F83" t="s">
         <v>96</v>
       </c>
       <c r="G83" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H83" s="2">
         <v>45774</v>
@@ -3661,10 +3682,10 @@
         <v>5</v>
       </c>
       <c r="R83" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -3672,19 +3693,19 @@
         <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D84" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F84" t="s">
         <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H84" s="2">
         <v>45774</v>
@@ -3693,10 +3714,10 @@
         <v>2</v>
       </c>
       <c r="R84" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T84" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -3710,7 +3731,7 @@
         <v>96</v>
       </c>
       <c r="G85" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H85" s="2">
         <v>45794</v>
@@ -3719,10 +3740,10 @@
         <v>45</v>
       </c>
       <c r="R85" t="s">
+        <v>252</v>
+      </c>
+      <c r="T85" t="s">
         <v>253</v>
-      </c>
-      <c r="T85" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -3730,7 +3751,7 @@
         <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D86" t="s">
         <v>105</v>
@@ -3739,7 +3760,7 @@
         <v>96</v>
       </c>
       <c r="G86" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H86" s="2">
         <v>45794</v>
@@ -3748,10 +3769,10 @@
         <v>50</v>
       </c>
       <c r="R86" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -3759,7 +3780,7 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D87" t="s">
         <v>101</v>
@@ -3768,7 +3789,7 @@
         <v>96</v>
       </c>
       <c r="G87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H87" s="2">
         <v>45794</v>
@@ -3777,10 +3798,10 @@
         <v>70</v>
       </c>
       <c r="R87" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -3797,7 +3818,7 @@
         <v>96</v>
       </c>
       <c r="G88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H88" s="2">
         <v>45809</v>
@@ -3806,10 +3827,10 @@
         <v>10</v>
       </c>
       <c r="R88" t="s">
+        <v>259</v>
+      </c>
+      <c r="T88" t="s">
         <v>260</v>
-      </c>
-      <c r="T88" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -3826,7 +3847,7 @@
         <v>96</v>
       </c>
       <c r="G89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H89" s="2">
         <v>45808</v>
@@ -3835,10 +3856,10 @@
         <v>40</v>
       </c>
       <c r="R89" t="s">
+        <v>261</v>
+      </c>
+      <c r="T89" t="s">
         <v>262</v>
-      </c>
-      <c r="T89" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -3852,7 +3873,7 @@
         <v>117</v>
       </c>
       <c r="G90" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H90" s="2">
         <v>45808</v>
@@ -3861,10 +3882,10 @@
         <v>0</v>
       </c>
       <c r="R90" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T90" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -3872,7 +3893,7 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F91" t="s">
         <v>96</v>
@@ -3887,7 +3908,7 @@
         <v>3.99</v>
       </c>
       <c r="T91" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -3895,7 +3916,7 @@
         <v>91</v>
       </c>
       <c r="C92" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D92" t="s">
         <v>105</v>
@@ -3904,7 +3925,7 @@
         <v>96</v>
       </c>
       <c r="G92" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H92" s="2">
         <v>45830</v>
@@ -3913,7 +3934,7 @@
         <v>100</v>
       </c>
       <c r="T92" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -3921,7 +3942,7 @@
         <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -3930,7 +3951,7 @@
         <v>96</v>
       </c>
       <c r="G93" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H93" s="2">
         <v>45927</v>
@@ -3939,7 +3960,7 @@
         <v>5</v>
       </c>
       <c r="T93" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -3947,13 +3968,13 @@
         <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
         <v>96</v>
       </c>
       <c r="G94" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H94" s="2">
         <v>45927</v>
@@ -3962,7 +3983,7 @@
         <v>10</v>
       </c>
       <c r="T94" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -3970,10 +3991,10 @@
         <v>94</v>
       </c>
       <c r="C95" t="s">
+        <v>285</v>
+      </c>
+      <c r="D95" t="s">
         <v>286</v>
-      </c>
-      <c r="D95" t="s">
-        <v>287</v>
       </c>
       <c r="F95" t="s">
         <v>96</v>
@@ -3988,10 +4009,10 @@
         <v>25</v>
       </c>
       <c r="R95" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T95" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -3999,7 +4020,7 @@
         <v>95</v>
       </c>
       <c r="C96" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="D96" t="s">
         <v>164</v>
@@ -4008,7 +4029,7 @@
         <v>96</v>
       </c>
       <c r="G96" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H96" s="2">
         <v>45976</v>
@@ -4017,11 +4038,152 @@
         <v>9.99</v>
       </c>
       <c r="T96" t="s">
-        <v>292</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="C97" t="s">
+        <v>297</v>
+      </c>
+      <c r="D97" t="s">
+        <v>164</v>
+      </c>
+      <c r="F97" t="s">
+        <v>96</v>
+      </c>
+      <c r="G97" t="s">
+        <v>190</v>
+      </c>
+      <c r="H97" s="2">
+        <v>46081</v>
+      </c>
+      <c r="J97" s="7">
+        <v>30</v>
+      </c>
+      <c r="T97" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="C98" t="s">
+        <v>301</v>
+      </c>
+      <c r="D98" t="s">
+        <v>164</v>
+      </c>
+      <c r="F98" t="s">
+        <v>96</v>
+      </c>
+      <c r="G98" t="s">
+        <v>190</v>
+      </c>
+      <c r="H98" s="2">
+        <v>46081</v>
+      </c>
+      <c r="J98" s="7">
+        <v>42</v>
+      </c>
+      <c r="T98" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="C99" t="s">
+        <v>301</v>
+      </c>
+      <c r="D99" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99" t="s">
+        <v>96</v>
+      </c>
+      <c r="G99" t="s">
+        <v>190</v>
+      </c>
+      <c r="H99" s="2">
+        <v>46081</v>
+      </c>
+      <c r="J99" s="7">
+        <v>42</v>
+      </c>
+      <c r="T99" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="D100" t="s">
+        <v>189</v>
+      </c>
+      <c r="F100" t="s">
+        <v>96</v>
+      </c>
+      <c r="G100" t="s">
+        <v>190</v>
+      </c>
+      <c r="H100" s="2">
+        <v>46081</v>
+      </c>
+      <c r="J100" s="7">
+        <v>12</v>
+      </c>
+      <c r="T100" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="D101" t="s">
+        <v>304</v>
+      </c>
+      <c r="F101" t="s">
+        <v>96</v>
+      </c>
+      <c r="G101" t="s">
+        <v>190</v>
+      </c>
+      <c r="H101" s="2">
+        <v>46081</v>
+      </c>
+      <c r="J101" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="D102" t="s">
+        <v>304</v>
+      </c>
+      <c r="F102" t="s">
+        <v>96</v>
+      </c>
+      <c r="G102" t="s">
+        <v>190</v>
+      </c>
+      <c r="H102" s="2">
+        <v>46081</v>
+      </c>
+      <c r="J102" s="7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U92">
+  <autoFilter ref="A1:U102">
     <filterColumn colId="3"/>
   </autoFilter>
   <sortState ref="A2:U72">
@@ -4041,7 +4203,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -5374,7 +5536,7 @@
         <v>119</v>
       </c>
       <c r="E96" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -5388,7 +5550,7 @@
         <v>119</v>
       </c>
       <c r="E97" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -5399,10 +5561,10 @@
         <v>45773</v>
       </c>
       <c r="C98" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" t="s">
         <v>230</v>
-      </c>
-      <c r="E98" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5413,10 +5575,10 @@
         <v>45788</v>
       </c>
       <c r="C99" t="s">
+        <v>242</v>
+      </c>
+      <c r="D99" t="s">
         <v>243</v>
-      </c>
-      <c r="D99" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5427,13 +5589,13 @@
         <v>45787</v>
       </c>
       <c r="C100" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" t="s">
         <v>245</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>246</v>
-      </c>
-      <c r="E100" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5444,13 +5606,13 @@
         <v>45787</v>
       </c>
       <c r="C101" t="s">
+        <v>244</v>
+      </c>
+      <c r="D101" t="s">
         <v>245</v>
       </c>
-      <c r="D101" t="s">
-        <v>246</v>
-      </c>
       <c r="E101" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5461,10 +5623,10 @@
         <v>45795</v>
       </c>
       <c r="C102" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D102" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5475,10 +5637,10 @@
         <v>45805</v>
       </c>
       <c r="C103" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D103" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5489,13 +5651,13 @@
         <v>45808</v>
       </c>
       <c r="C104" t="s">
+        <v>264</v>
+      </c>
+      <c r="D104" t="s">
         <v>265</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>266</v>
-      </c>
-      <c r="E104" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5506,13 +5668,13 @@
         <v>45808</v>
       </c>
       <c r="C105" t="s">
+        <v>264</v>
+      </c>
+      <c r="D105" t="s">
         <v>265</v>
       </c>
-      <c r="D105" t="s">
-        <v>266</v>
-      </c>
       <c r="E105" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5526,10 +5688,10 @@
         <v>85</v>
       </c>
       <c r="D106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E106" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5543,10 +5705,10 @@
         <v>85</v>
       </c>
       <c r="D107" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E107" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5560,7 +5722,7 @@
         <v>118</v>
       </c>
       <c r="D108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5574,7 +5736,7 @@
         <v>85</v>
       </c>
       <c r="D109" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5585,10 +5747,10 @@
         <v>45886</v>
       </c>
       <c r="C110" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5602,10 +5764,10 @@
         <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E111" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5619,7 +5781,7 @@
         <v>84</v>
       </c>
       <c r="E112" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5633,7 +5795,7 @@
         <v>84</v>
       </c>
       <c r="E113" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5644,7 +5806,7 @@
         <v>45976</v>
       </c>
       <c r="C114" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5655,7 +5817,7 @@
         <v>45976</v>
       </c>
       <c r="C115" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5669,7 +5831,7 @@
         <v>118</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5683,7 +5845,7 @@
         <v>84</v>
       </c>
       <c r="E117" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5694,7 +5856,71 @@
         <v>45983</v>
       </c>
       <c r="C118" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>9</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C119" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
+        <v>35</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C120" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>23</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46090</v>
+      </c>
+      <c r="C121" t="s">
+        <v>118</v>
+      </c>
+      <c r="D121" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>86</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C122" t="s">
+        <v>84</v>
+      </c>
+      <c r="D122" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>96</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C123" t="s">
+        <v>84</v>
+      </c>
+      <c r="D123" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="307">
   <si>
     <t>id</t>
   </si>
@@ -448,15 +448,6 @@
   </si>
   <si>
     <t>Arbre_76_2025-03-01.jpg</t>
-  </si>
-  <si>
-    <t>Arbre_77_2025-03-01.jpg</t>
-  </si>
-  <si>
-    <t>Arbre_78_2025-03-01.jpg</t>
-  </si>
-  <si>
-    <t>Arbre_79_2025-03-01.jpg</t>
   </si>
   <si>
     <t>Arbre_80_2025-03-10.jpg</t>
@@ -941,6 +932,21 @@
   </si>
   <si>
     <t>Cognassier du Japon</t>
+  </si>
+  <si>
+    <t>Arbre_100_2025-03-18.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_101_2025-03-18.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_77_2025-06-22_Taille_Atelier.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_79_2025-06-22_Taille_Atelier_2.jpg</t>
+  </si>
+  <si>
+    <t>Arbre_78_2025-05-18_fleurs.jpg</t>
   </si>
 </sst>
 </file>
@@ -1237,10 +1243,10 @@
         <v>107</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M1" s="13" t="s">
         <v>122</v>
@@ -1272,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>96</v>
@@ -1310,7 +1316,7 @@
         <v>96</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H3" s="15">
         <v>45591</v>
@@ -1333,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>96</v>
@@ -1362,10 +1368,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>96</v>
@@ -1385,7 +1391,7 @@
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
       <c r="S5" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T5" s="8" t="s">
         <v>47</v>
@@ -1396,10 +1402,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>96</v>
@@ -1422,16 +1428,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>99</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H7" s="15">
         <v>45200</v>
@@ -1455,16 +1461,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H8" s="15">
         <v>44835</v>
@@ -1486,10 +1492,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>96</v>
@@ -1517,16 +1523,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H10" s="2">
         <v>44842</v>
@@ -1545,19 +1551,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
@@ -1576,16 +1582,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
@@ -1596,7 +1602,7 @@
         <v>2024</v>
       </c>
       <c r="S12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T12" t="s">
         <v>16</v>
@@ -1607,13 +1613,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
@@ -1632,19 +1638,19 @@
         <v>13</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>117</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
@@ -1663,19 +1669,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H15" s="2">
         <v>45535</v>
@@ -1694,19 +1700,19 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" t="s">
         <v>145</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" t="s">
-        <v>148</v>
       </c>
       <c r="H16" s="2">
         <v>45591</v>
@@ -1720,7 +1726,7 @@
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="T16" t="s">
         <v>20</v>
@@ -1731,16 +1737,16 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
         <v>96</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J17" s="7">
         <v>10</v>
@@ -1762,13 +1768,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F18" t="s">
         <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H18" s="2">
         <v>45261</v>
@@ -1793,7 +1799,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F19" t="s">
         <v>96</v>
@@ -1812,7 +1818,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F20" t="s">
         <v>96</v>
@@ -1837,16 +1843,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F21" t="s">
         <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
@@ -1862,13 +1868,13 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F22" t="s">
         <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
@@ -1884,13 +1890,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F23" t="s">
         <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J23" s="7">
         <v>50</v>
@@ -1904,7 +1910,7 @@
         <v>-0.5</v>
       </c>
       <c r="S23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="T23" t="s">
         <v>28</v>
@@ -1918,7 +1924,7 @@
         <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F24" t="s">
         <v>96</v>
@@ -1946,13 +1952,13 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F25" t="s">
         <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
@@ -1980,7 +1986,7 @@
         <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H26" s="2">
         <v>45584</v>
@@ -2014,7 +2020,7 @@
         <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H27" s="2">
         <v>45584</v>
@@ -2045,7 +2051,7 @@
         <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H28" s="2">
         <v>45413</v>
@@ -2059,7 +2065,7 @@
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="T28" t="s">
         <v>33</v>
@@ -2070,7 +2076,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D29" t="s">
         <v>105</v>
@@ -2079,13 +2085,13 @@
         <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H29" s="2">
         <v>45420</v>
       </c>
       <c r="I29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J29" s="7">
         <v>100</v>
@@ -2104,16 +2110,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F30" t="s">
         <v>96</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H30" s="2">
         <v>44982</v>
@@ -2127,7 +2133,7 @@
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="S30" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T30" t="s">
         <v>35</v>
@@ -2138,16 +2144,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D31" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
         <v>99</v>
       </c>
       <c r="G31" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J31" s="7">
         <v>30</v>
@@ -2169,19 +2175,19 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F32" t="s">
         <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H32" s="2">
         <v>45339</v>
@@ -2195,10 +2201,10 @@
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" t="s">
+        <v>190</v>
+      </c>
+      <c r="S32" t="s">
         <v>193</v>
-      </c>
-      <c r="S32" t="s">
-        <v>196</v>
       </c>
       <c r="T32" t="s">
         <v>38</v>
@@ -2209,19 +2215,19 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F33" t="s">
         <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H33" s="2">
         <v>45339</v>
@@ -2235,10 +2241,10 @@
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
       <c r="R33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="S33" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="T33" t="s">
         <v>39</v>
@@ -2249,13 +2255,13 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F34" t="s">
         <v>117</v>
       </c>
       <c r="G34" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H34" s="2">
         <v>44896</v>
@@ -2274,13 +2280,13 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F35" t="s">
         <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H35" s="2">
         <v>45339</v>
@@ -2308,7 +2314,7 @@
         <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H36" s="2">
         <v>44982</v>
@@ -2319,7 +2325,7 @@
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="S36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="T36" t="s">
         <v>42</v>
@@ -2330,13 +2336,13 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F37" t="s">
         <v>99</v>
       </c>
       <c r="G37" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H37" s="2">
         <v>45200</v>
@@ -2358,13 +2364,13 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F38" t="s">
         <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
@@ -2383,13 +2389,13 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F39" t="s">
         <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H39" s="2">
         <v>44982</v>
@@ -2411,13 +2417,13 @@
         <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F40" t="s">
         <v>96</v>
       </c>
       <c r="G40" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
@@ -2425,10 +2431,10 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="S40" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s">
         <v>46</v>
@@ -2504,7 +2510,7 @@
         <v>99</v>
       </c>
       <c r="G43" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H43" s="2">
         <v>45200</v>
@@ -2526,16 +2532,16 @@
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E44" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F44" t="s">
         <v>99</v>
       </c>
       <c r="G44" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H44" s="2">
         <v>45200</v>
@@ -2557,16 +2563,16 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F45" t="s">
         <v>117</v>
       </c>
       <c r="G45" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H45" s="2">
         <v>44896</v>
@@ -2585,13 +2591,13 @@
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H46" s="2">
         <v>44989</v>
@@ -2613,7 +2619,7 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -2641,13 +2647,13 @@
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H48" s="2">
         <v>45206</v>
@@ -2669,10 +2675,10 @@
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F49" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J49" s="7">
         <v>0</v>
@@ -2686,7 +2692,7 @@
         <v>2023</v>
       </c>
       <c r="S49" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="T49" t="s">
         <v>56</v>
@@ -2703,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H50" s="2">
         <v>45206</v>
@@ -2731,7 +2737,7 @@
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H51" s="2">
         <v>45206</v>
@@ -2753,13 +2759,13 @@
         <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F52" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J52" s="7">
         <v>0</v>
@@ -2781,16 +2787,16 @@
         <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E53" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H53" s="2">
         <v>45206</v>
@@ -2812,13 +2818,13 @@
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H54" s="2">
         <v>45971</v>
@@ -2832,7 +2838,7 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="R54" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T54" t="s">
         <v>62</v>
@@ -2843,13 +2849,13 @@
         <v>54</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>117</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H55" s="19">
         <v>45207</v>
@@ -2876,13 +2882,13 @@
         <v>55</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H56" s="2">
         <v>45206</v>
@@ -2904,19 +2910,19 @@
         <v>57</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E57" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H57" s="2">
         <v>45971</v>
@@ -2938,16 +2944,16 @@
         <v>58</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H58" s="2">
         <v>45971</v>
@@ -2969,16 +2975,16 @@
         <v>59</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H59" s="2">
         <v>45971</v>
@@ -3000,13 +3006,13 @@
         <v>60</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H60" s="2">
         <v>45206</v>
@@ -3028,13 +3034,13 @@
         <v>61</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H61" s="2">
         <v>45206</v>
@@ -3056,13 +3062,13 @@
         <v>62</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H62" s="2">
         <v>45206</v>
@@ -3084,7 +3090,7 @@
         <v>63</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -3101,7 +3107,7 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
       <c r="R63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="T63" t="s">
         <v>72</v>
@@ -3112,7 +3118,7 @@
         <v>64</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
@@ -3129,10 +3135,10 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
       <c r="R64" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="S64" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="T64" t="s">
         <v>73</v>
@@ -3143,7 +3149,7 @@
         <v>65</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
@@ -3152,7 +3158,7 @@
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H65" s="2">
         <v>44989</v>
@@ -3174,13 +3180,13 @@
         <v>66</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H66" s="2">
         <v>44989</v>
@@ -3202,13 +3208,13 @@
         <v>67</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H67" s="2">
         <v>44989</v>
@@ -3222,7 +3228,7 @@
       <c r="P67" s="9"/>
       <c r="Q67" s="9"/>
       <c r="T67" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -3230,13 +3236,13 @@
         <v>68</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H68" s="2">
         <v>44989</v>
@@ -3258,13 +3264,13 @@
         <v>69</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H69" s="2">
         <v>44989</v>
@@ -3286,10 +3292,10 @@
         <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F70" t="s">
         <v>96</v>
@@ -3318,10 +3324,10 @@
         <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F71" t="s">
         <v>96</v>
@@ -3342,7 +3348,7 @@
       <c r="P71" s="9"/>
       <c r="Q71" s="9"/>
       <c r="T71" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -3426,7 +3432,7 @@
       <c r="P74" s="9"/>
       <c r="Q74" s="9"/>
       <c r="T74" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -3508,7 +3514,7 @@
         <v>70</v>
       </c>
       <c r="T77" t="s">
-        <v>141</v>
+        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -3543,7 +3549,7 @@
         <v>115</v>
       </c>
       <c r="T78" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -3572,7 +3578,7 @@
         <v>35</v>
       </c>
       <c r="T79" t="s">
-        <v>143</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -3583,7 +3589,7 @@
         <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F80" t="s">
         <v>117</v>
@@ -3598,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="R80" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="T80" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -3609,16 +3615,16 @@
         <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D81" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F81" t="s">
         <v>96</v>
       </c>
       <c r="G81" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H81" s="2">
         <v>45774</v>
@@ -3627,7 +3633,7 @@
         <v>20</v>
       </c>
       <c r="T81" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -3635,16 +3641,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D82" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F82" t="s">
         <v>117</v>
       </c>
       <c r="G82" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H82" s="2">
         <v>45774</v>
@@ -3653,10 +3659,10 @@
         <v>0</v>
       </c>
       <c r="R82" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="T82" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -3664,16 +3670,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D83" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F83" t="s">
         <v>96</v>
       </c>
       <c r="G83" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H83" s="2">
         <v>45774</v>
@@ -3682,10 +3688,10 @@
         <v>5</v>
       </c>
       <c r="R83" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="T83" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -3693,19 +3699,19 @@
         <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D84" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E84" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F84" t="s">
         <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H84" s="2">
         <v>45774</v>
@@ -3714,10 +3720,10 @@
         <v>2</v>
       </c>
       <c r="R84" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="T84" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -3731,7 +3737,7 @@
         <v>96</v>
       </c>
       <c r="G85" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H85" s="2">
         <v>45794</v>
@@ -3740,10 +3746,10 @@
         <v>45</v>
       </c>
       <c r="R85" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="T85" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -3751,7 +3757,7 @@
         <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D86" t="s">
         <v>105</v>
@@ -3760,7 +3766,7 @@
         <v>96</v>
       </c>
       <c r="G86" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H86" s="2">
         <v>45794</v>
@@ -3769,10 +3775,10 @@
         <v>50</v>
       </c>
       <c r="R86" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="T86" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -3780,7 +3786,7 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D87" t="s">
         <v>101</v>
@@ -3789,7 +3795,7 @@
         <v>96</v>
       </c>
       <c r="G87" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H87" s="2">
         <v>45794</v>
@@ -3798,10 +3804,10 @@
         <v>70</v>
       </c>
       <c r="R87" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="T87" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -3809,16 +3815,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F88" t="s">
         <v>96</v>
       </c>
       <c r="G88" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H88" s="2">
         <v>45809</v>
@@ -3827,10 +3833,10 @@
         <v>10</v>
       </c>
       <c r="R88" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="T88" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -3847,7 +3853,7 @@
         <v>96</v>
       </c>
       <c r="G89" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H89" s="2">
         <v>45808</v>
@@ -3856,10 +3862,10 @@
         <v>40</v>
       </c>
       <c r="R89" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -3867,13 +3873,13 @@
         <v>89</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F90" t="s">
         <v>117</v>
       </c>
       <c r="G90" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H90" s="2">
         <v>45808</v>
@@ -3882,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="R90" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="T90" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -3893,13 +3899,13 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F91" t="s">
         <v>96</v>
       </c>
       <c r="G91" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H91" s="2">
         <v>45824</v>
@@ -3908,7 +3914,7 @@
         <v>3.99</v>
       </c>
       <c r="T91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -3916,7 +3922,7 @@
         <v>91</v>
       </c>
       <c r="C92" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D92" t="s">
         <v>105</v>
@@ -3925,7 +3931,7 @@
         <v>96</v>
       </c>
       <c r="G92" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H92" s="2">
         <v>45830</v>
@@ -3934,7 +3940,7 @@
         <v>100</v>
       </c>
       <c r="T92" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -3942,16 +3948,16 @@
         <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F93" t="s">
         <v>96</v>
       </c>
       <c r="G93" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H93" s="2">
         <v>45927</v>
@@ -3960,7 +3966,7 @@
         <v>5</v>
       </c>
       <c r="T93" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -3968,13 +3974,13 @@
         <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F94" t="s">
         <v>96</v>
       </c>
       <c r="G94" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H94" s="2">
         <v>45927</v>
@@ -3983,7 +3989,7 @@
         <v>10</v>
       </c>
       <c r="T94" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -3991,16 +3997,16 @@
         <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D95" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F95" t="s">
         <v>96</v>
       </c>
       <c r="G95" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H95" s="2">
         <v>45962</v>
@@ -4009,10 +4015,10 @@
         <v>25</v>
       </c>
       <c r="R95" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="T95" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -4020,16 +4026,16 @@
         <v>95</v>
       </c>
       <c r="C96" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D96" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F96" t="s">
         <v>96</v>
       </c>
       <c r="G96" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H96" s="2">
         <v>45976</v>
@@ -4038,7 +4044,7 @@
         <v>9.99</v>
       </c>
       <c r="T96" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -4046,16 +4052,16 @@
         <v>96</v>
       </c>
       <c r="C97" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D97" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F97" t="s">
         <v>96</v>
       </c>
       <c r="G97" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H97" s="2">
         <v>46081</v>
@@ -4064,7 +4070,7 @@
         <v>30</v>
       </c>
       <c r="T97" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -4072,16 +4078,16 @@
         <v>97</v>
       </c>
       <c r="C98" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D98" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F98" t="s">
         <v>96</v>
       </c>
       <c r="G98" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H98" s="2">
         <v>46081</v>
@@ -4090,7 +4096,7 @@
         <v>42</v>
       </c>
       <c r="T98" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -4098,16 +4104,16 @@
         <v>98</v>
       </c>
       <c r="C99" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D99" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F99" t="s">
         <v>96</v>
       </c>
       <c r="G99" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H99" s="2">
         <v>46081</v>
@@ -4116,7 +4122,7 @@
         <v>42</v>
       </c>
       <c r="T99" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -4124,13 +4130,13 @@
         <v>99</v>
       </c>
       <c r="D100" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F100" t="s">
         <v>96</v>
       </c>
       <c r="G100" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H100" s="2">
         <v>46081</v>
@@ -4139,7 +4145,7 @@
         <v>12</v>
       </c>
       <c r="T100" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -4147,19 +4153,22 @@
         <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F101" t="s">
         <v>96</v>
       </c>
       <c r="G101" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H101" s="2">
         <v>46081</v>
       </c>
       <c r="J101" s="7">
         <v>10</v>
+      </c>
+      <c r="T101" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -4167,19 +4176,22 @@
         <v>101</v>
       </c>
       <c r="D102" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F102" t="s">
         <v>96</v>
       </c>
       <c r="G102" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H102" s="2">
         <v>46081</v>
       </c>
       <c r="J102" s="7">
         <v>10</v>
+      </c>
+      <c r="T102" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -5522,7 +5534,7 @@
         <v>85</v>
       </c>
       <c r="D95" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -5536,7 +5548,7 @@
         <v>119</v>
       </c>
       <c r="E96" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -5550,7 +5562,7 @@
         <v>119</v>
       </c>
       <c r="E97" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -5561,10 +5573,10 @@
         <v>45773</v>
       </c>
       <c r="C98" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E98" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5575,10 +5587,10 @@
         <v>45788</v>
       </c>
       <c r="C99" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D99" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5589,13 +5601,13 @@
         <v>45787</v>
       </c>
       <c r="C100" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D100" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E100" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5606,13 +5618,13 @@
         <v>45787</v>
       </c>
       <c r="C101" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D101" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E101" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5623,10 +5635,10 @@
         <v>45795</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D102" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5637,10 +5649,10 @@
         <v>45805</v>
       </c>
       <c r="C103" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D103" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5651,13 +5663,13 @@
         <v>45808</v>
       </c>
       <c r="C104" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D104" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E104" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5668,18 +5680,18 @@
         <v>45808</v>
       </c>
       <c r="C105" t="s">
+        <v>261</v>
+      </c>
+      <c r="D105" t="s">
+        <v>262</v>
+      </c>
+      <c r="E105" t="s">
         <v>264</v>
-      </c>
-      <c r="D105" t="s">
-        <v>265</v>
-      </c>
-      <c r="E105" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B106" s="2">
         <v>45830</v>
@@ -5688,10 +5700,10 @@
         <v>85</v>
       </c>
       <c r="D106" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E106" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5705,10 +5717,10 @@
         <v>85</v>
       </c>
       <c r="D107" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E107" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5722,7 +5734,7 @@
         <v>118</v>
       </c>
       <c r="D108" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5736,7 +5748,7 @@
         <v>85</v>
       </c>
       <c r="D109" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5747,10 +5759,10 @@
         <v>45886</v>
       </c>
       <c r="C110" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D110" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5764,10 +5776,10 @@
         <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E111" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5781,7 +5793,7 @@
         <v>84</v>
       </c>
       <c r="E112" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5795,7 +5807,7 @@
         <v>84</v>
       </c>
       <c r="E113" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5806,7 +5818,7 @@
         <v>45976</v>
       </c>
       <c r="C114" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5817,7 +5829,7 @@
         <v>45976</v>
       </c>
       <c r="C115" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5831,7 +5843,7 @@
         <v>118</v>
       </c>
       <c r="D116" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5845,7 +5857,7 @@
         <v>84</v>
       </c>
       <c r="E117" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5856,7 +5868,7 @@
         <v>45983</v>
       </c>
       <c r="C118" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5867,7 +5879,7 @@
         <v>46089</v>
       </c>
       <c r="C119" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5878,7 +5890,7 @@
         <v>46089</v>
       </c>
       <c r="C120" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5892,7 +5904,7 @@
         <v>118</v>
       </c>
       <c r="D121" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5906,7 +5918,7 @@
         <v>84</v>
       </c>
       <c r="D122" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5920,7 +5932,7 @@
         <v>84</v>
       </c>
       <c r="D123" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Mode-emploi" sheetId="3" r:id="rId1"/>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="313">
   <si>
     <t>id</t>
   </si>
@@ -947,6 +947,24 @@
   </si>
   <si>
     <t>Arbre_78_2025-05-18_fleurs.jpg</t>
+  </si>
+  <si>
+    <t>Marcotte</t>
+  </si>
+  <si>
+    <t>Marcotte de l'arbre 68</t>
+  </si>
+  <si>
+    <t>Arbre_102_2026-04-26.jpg</t>
+  </si>
+  <si>
+    <t>Fin Marcotte</t>
+  </si>
+  <si>
+    <t>Création de l'arbre 102</t>
+  </si>
+  <si>
+    <t>Issue de l'arbre 68</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1212,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:T102"/>
+  <dimension ref="A1:T103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.77734375" bestFit="1" customWidth="1"/>
@@ -4192,6 +4210,37 @@
       </c>
       <c r="T102" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F103" t="s">
+        <v>307</v>
+      </c>
+      <c r="G103" t="s">
+        <v>209</v>
+      </c>
+      <c r="H103" s="2">
+        <v>46158</v>
+      </c>
+      <c r="J103" s="7">
+        <v>0</v>
+      </c>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
+      <c r="O103" s="9"/>
+      <c r="P103" s="9"/>
+      <c r="Q103" s="9"/>
+      <c r="R103" t="s">
+        <v>308</v>
+      </c>
+      <c r="T103" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4215,7 +4264,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -5935,6 +5984,34 @@
         <v>295</v>
       </c>
     </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>68</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C124" t="s">
+        <v>310</v>
+      </c>
+      <c r="D124" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>102</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C125" t="s">
+        <v>307</v>
+      </c>
+      <c r="D125" t="s">
+        <v>312</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E116">
     <filterColumn colId="2"/>

--- a/data/Suivi_bonsais_Laeti.xlsx
+++ b/data/Suivi_bonsais_Laeti.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mode-emploi" sheetId="3" r:id="rId1"/>
@@ -955,9 +955,6 @@
     <t>Marcotte de l'arbre 68</t>
   </si>
   <si>
-    <t>Arbre_102_2026-04-26.jpg</t>
-  </si>
-  <si>
     <t>Fin Marcotte</t>
   </si>
   <si>
@@ -965,6 +962,9 @@
   </si>
   <si>
     <t>Issue de l'arbre 68</t>
+  </si>
+  <si>
+    <t>Arbre_102_2026-05-16.jpg</t>
   </si>
 </sst>
 </file>
@@ -4240,7 +4240,7 @@
         <v>308</v>
       </c>
       <c r="T103" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -5992,10 +5992,10 @@
         <v>46158</v>
       </c>
       <c r="C124" t="s">
+        <v>309</v>
+      </c>
+      <c r="D124" t="s">
         <v>310</v>
-      </c>
-      <c r="D124" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -6009,7 +6009,7 @@
         <v>307</v>
       </c>
       <c r="D125" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
